--- a/data/SBKnowledgeData.xlsx
+++ b/data/SBKnowledgeData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OsamuKoga\09_資格試験\宅建士\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\SBFlash\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CFC14F-66D1-4035-BD1F-5C7B20F492A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70B71DC-E270-4E48-948D-EBAD8474EBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30945" yWindow="2610" windowWidth="19815" windowHeight="9525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30135" yWindow="3990" windowWidth="23550" windowHeight="9015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宅建業法" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="426">
   <si>
     <t>№</t>
   </si>
@@ -1332,6 +1332,13 @@
     </rPh>
     <rPh sb="24" eb="26">
       <t>キメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>語呂合わせ</t>
+    <rPh sb="0" eb="3">
+      <t>ゴロア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1426,7 +1433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1444,6 +1451,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1724,20 +1737,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
     <col min="2" max="2" width="40.625" customWidth="1"/>
     <col min="3" max="3" width="44.375" style="3" customWidth="1"/>
-    <col min="4" max="5" width="26.125" customWidth="1"/>
-    <col min="6" max="6" width="50.5" customWidth="1"/>
-    <col min="7" max="7" width="22.25" customWidth="1"/>
-    <col min="8" max="8" width="19.75" customWidth="1"/>
-    <col min="9" max="9" width="19.375" customWidth="1"/>
+    <col min="4" max="4" width="39.875" style="3" customWidth="1"/>
+    <col min="5" max="6" width="26.125" customWidth="1"/>
+    <col min="7" max="7" width="50.5" customWidth="1"/>
+    <col min="8" max="8" width="22.25" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
+    <col min="10" max="10" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1748,25 +1762,28 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1778,18 +1795,19 @@
         <f>IF($A2="","",VLOOKUP($A2,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2"/>
       <c r="E2" s="5"/>
-      <c r="F2" t="str">
+      <c r="F2" s="5"/>
+      <c r="G2" t="str">
         <f>IF($A2="","",VLOOKUP($A2,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は道路・公園など公共施設を除き宅地となる</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <f>IF($A2="","",VLOOKUP($A2,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は道路・公園など公共施設を除き宅地となる</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -1801,18 +1819,19 @@
         <f>IF($A3="","",VLOOKUP($A3,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3"/>
       <c r="E3" s="5"/>
-      <c r="F3" t="str">
+      <c r="F3" s="5"/>
+      <c r="G3" t="str">
         <f>IF($A3="","",VLOOKUP($A3,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は現況に関係なく宅地となる</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <f>IF($A3="","",VLOOKUP($A3,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は現況に関係なく宅地となる</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -1824,18 +1843,19 @@
         <f>IF($A4="","",VLOOKUP($A4,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4"/>
       <c r="E4" s="5"/>
-      <c r="F4" t="str">
+      <c r="F4" s="5"/>
+      <c r="G4" t="str">
         <f>IF($A4="","",VLOOKUP($A4,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域外でも建物敷地として使用される土地は宅地</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <f>IF($A4="","",VLOOKUP($A4,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域外でも建物敷地として使用される土地は宅地</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -1847,18 +1867,19 @@
         <f>IF($A5="","",VLOOKUP($A5,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5"/>
       <c r="E5" s="5"/>
-      <c r="F5" t="str">
+      <c r="F5" s="5"/>
+      <c r="G5" t="str">
         <f>IF($A5="","",VLOOKUP($A5,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>道路・河川・公園など公共施設の用地は宅地ではない</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <f>IF($A5="","",VLOOKUP($A5,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>道路・河川・公園など公共施設の用地は宅地ではない</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -1870,18 +1891,19 @@
         <f>IF($A6="","",VLOOKUP($A6,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6"/>
       <c r="E6" s="5"/>
-      <c r="F6" t="str">
+      <c r="F6" s="5"/>
+      <c r="G6" t="str">
         <f>IF($A6="","",VLOOKUP($A6,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>建物敷地以外でも宅地に該当する場合がある</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <f>IF($A6="","",VLOOKUP($A6,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>建物敷地以外でも宅地に該当する場合がある</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -1893,18 +1915,19 @@
         <f>IF($A7="","",VLOOKUP($A7,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7"/>
       <c r="E7" s="5"/>
-      <c r="F7" t="str">
+      <c r="F7" s="5"/>
+      <c r="G7" t="str">
         <f>IF($A7="","",VLOOKUP($A7,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業は反復継続が必要</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <f>IF($A7="","",VLOOKUP($A7,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業は反復継続が必要</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -1916,18 +1939,19 @@
         <f>IF($A8="","",VLOOKUP($A8,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8"/>
       <c r="E8" s="5"/>
-      <c r="F8" t="str">
+      <c r="F8" s="5"/>
+      <c r="G8" t="str">
         <f>IF($A8="","",VLOOKUP($A8,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>反復継続して売買する場合は宅建業</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <f>IF($A8="","",VLOOKUP($A8,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>反復継続して売買する場合は宅建業</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -1939,18 +1963,19 @@
         <f>IF($A9="","",VLOOKUP($A9,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9"/>
       <c r="E9" s="5"/>
-      <c r="F9" t="str">
+      <c r="F9" s="5"/>
+      <c r="G9" t="str">
         <f>IF($A9="","",VLOOKUP($A9,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>賃貸の代理・媒介は宅建業</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <f>IF($A9="","",VLOOKUP($A9,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>賃貸の代理・媒介は宅建業</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -1962,18 +1987,19 @@
         <f>IF($A10="","",VLOOKUP($A10,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10"/>
       <c r="E10" s="5"/>
-      <c r="F10" t="str">
+      <c r="F10" s="5"/>
+      <c r="G10" t="str">
         <f>IF($A10="","",VLOOKUP($A10,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>貸借は宅建業に含まれない</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <f>IF($A10="","",VLOOKUP($A10,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>貸借は宅建業に含まれない</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -1985,18 +2011,19 @@
         <f>IF($A11="","",VLOOKUP($A11,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11"/>
       <c r="E11" s="5"/>
-      <c r="F11" t="str">
+      <c r="F11" s="5"/>
+      <c r="G11" t="str">
         <f>IF($A11="","",VLOOKUP($A11,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売買の媒介は宅建業</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <f>IF($A11="","",VLOOKUP($A11,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売買の媒介は宅建業</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -2008,18 +2035,19 @@
         <f>IF($A12="","",VLOOKUP($A12,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12"/>
       <c r="E12" s="5"/>
-      <c r="F12" t="str">
+      <c r="F12" s="5"/>
+      <c r="G12" t="str">
         <f>IF($A12="","",VLOOKUP($A12,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業免許は5年ごと更新</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <f>IF($A12="","",VLOOKUP($A12,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業免許は5年ごと更新</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -2031,18 +2059,19 @@
         <f>IF($A13="","",VLOOKUP($A13,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13"/>
       <c r="E13" s="5"/>
-      <c r="F13" t="str">
+      <c r="F13" s="5"/>
+      <c r="G13" t="str">
         <f>IF($A13="","",VLOOKUP($A13,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>満了前に申請必要</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <f>IF($A13="","",VLOOKUP($A13,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>満了前に申請必要</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -2054,18 +2083,19 @@
         <f>IF($A14="","",VLOOKUP($A14,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14"/>
       <c r="E14" s="5"/>
-      <c r="F14" t="str">
+      <c r="F14" s="5"/>
+      <c r="G14" t="str">
         <f>IF($A14="","",VLOOKUP($A14,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>複数都道府県は大臣免許</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <f>IF($A14="","",VLOOKUP($A14,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>複数都道府県は大臣免許</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -2077,18 +2107,19 @@
         <f>IF($A15="","",VLOOKUP($A15,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15"/>
       <c r="E15" s="5"/>
-      <c r="F15" t="str">
+      <c r="F15" s="5"/>
+      <c r="G15" t="str">
         <f>IF($A15="","",VLOOKUP($A15,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>単一都道府県は知事免許</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <f>IF($A15="","",VLOOKUP($A15,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>単一都道府県は知事免許</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -2100,18 +2131,19 @@
         <f>IF($A16="","",VLOOKUP($A16,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16"/>
       <c r="E16" s="5"/>
-      <c r="F16" t="str">
+      <c r="F16" s="5"/>
+      <c r="G16" t="str">
         <f>IF($A16="","",VLOOKUP($A16,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>免許が必要</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <f>IF($A16="","",VLOOKUP($A16,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>免許が必要</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -2123,18 +2155,19 @@
         <f>IF($A17="","",VLOOKUP($A17,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="D17"/>
       <c r="E17" s="5"/>
-      <c r="F17" t="str">
+      <c r="F17" s="5"/>
+      <c r="G17" t="str">
         <f>IF($A17="","",VLOOKUP($A17,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士が説明</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <f>IF($A17="","",VLOOKUP($A17,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士が説明</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -2146,18 +2179,19 @@
         <f>IF($A18="","",VLOOKUP($A18,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18"/>
       <c r="E18" s="5"/>
-      <c r="F18" t="str">
+      <c r="F18" s="5"/>
+      <c r="G18" t="str">
         <f>IF($A18="","",VLOOKUP($A18,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明が必要</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <f>IF($A18="","",VLOOKUP($A18,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明が必要</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -2169,18 +2203,19 @@
         <f>IF($A19="","",VLOOKUP($A19,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19"/>
       <c r="E19" s="5"/>
-      <c r="F19" t="str">
+      <c r="F19" s="5"/>
+      <c r="G19" t="str">
         <f>IF($A19="","",VLOOKUP($A19,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>5年</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <f>IF($A19="","",VLOOKUP($A19,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>5年</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -2192,18 +2227,19 @@
         <f>IF($A20="","",VLOOKUP($A20,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20"/>
       <c r="E20" s="5"/>
-      <c r="F20" t="str">
+      <c r="F20" s="5"/>
+      <c r="G20" t="str">
         <f>IF($A20="","",VLOOKUP($A20,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>法定講習必要</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <f>IF($A20="","",VLOOKUP($A20,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>法定講習必要</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -2215,18 +2251,19 @@
         <f>IF($A21="","",VLOOKUP($A21,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21"/>
       <c r="E21" s="5"/>
-      <c r="F21" t="str">
+      <c r="F21" s="5"/>
+      <c r="G21" t="str">
         <f>IF($A21="","",VLOOKUP($A21,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士のみ</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <f>IF($A21="","",VLOOKUP($A21,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士のみ</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>79</v>
       </c>
@@ -2238,18 +2275,19 @@
         <f>IF($A22="","",VLOOKUP($A22,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D22" s="5"/>
+      <c r="D22"/>
       <c r="E22" s="5"/>
-      <c r="F22" t="str">
+      <c r="F22" s="5"/>
+      <c r="G22" t="str">
         <f>IF($A22="","",VLOOKUP($A22,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>主事務所1000万</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <f>IF($A22="","",VLOOKUP($A22,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>主事務所1000万</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -2261,18 +2299,19 @@
         <f>IF($A23="","",VLOOKUP($A23,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D23" s="5"/>
+      <c r="D23"/>
       <c r="E23" s="5"/>
-      <c r="F23" t="str">
+      <c r="F23" s="5"/>
+      <c r="G23" t="str">
         <f>IF($A23="","",VLOOKUP($A23,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>500万</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <f>IF($A23="","",VLOOKUP($A23,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>500万</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>81</v>
       </c>
@@ -2284,18 +2323,19 @@
         <f>IF($A24="","",VLOOKUP($A24,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24"/>
       <c r="E24" s="5"/>
-      <c r="F24" t="str">
+      <c r="F24" s="5"/>
+      <c r="G24" t="str">
         <f>IF($A24="","",VLOOKUP($A24,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>届出必要</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
         <f>IF($A24="","",VLOOKUP($A24,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>届出必要</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -2307,18 +2347,19 @@
         <f>IF($A25="","",VLOOKUP($A25,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D25" s="5"/>
+      <c r="D25"/>
       <c r="E25" s="5"/>
-      <c r="F25" t="str">
+      <c r="F25" s="5"/>
+      <c r="G25" t="str">
         <f>IF($A25="","",VLOOKUP($A25,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>分担金制度</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <f>IF($A25="","",VLOOKUP($A25,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>分担金制度</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -2330,18 +2371,19 @@
         <f>IF($A26="","",VLOOKUP($A26,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D26" s="5"/>
+      <c r="D26"/>
       <c r="E26" s="5"/>
-      <c r="F26" t="str">
+      <c r="F26" s="5"/>
+      <c r="G26" t="str">
         <f>IF($A26="","",VLOOKUP($A26,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>1団体のみ</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <f>IF($A26="","",VLOOKUP($A26,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>1団体のみ</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -2353,18 +2395,19 @@
         <f>IF($A27="","",VLOOKUP($A27,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27"/>
       <c r="E27" s="5"/>
-      <c r="F27" t="str">
+      <c r="F27" s="5"/>
+      <c r="G27" t="str">
         <f>IF($A27="","",VLOOKUP($A27,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約前</v>
       </c>
-      <c r="H27" t="str">
+      <c r="I27" t="str">
         <f>IF($A27="","",VLOOKUP($A27,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約前</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>85</v>
       </c>
@@ -2376,18 +2419,19 @@
         <f>IF($A28="","",VLOOKUP($A28,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D28" s="5"/>
+      <c r="D28"/>
       <c r="E28" s="5"/>
-      <c r="F28" t="str">
+      <c r="F28" s="5"/>
+      <c r="G28" t="str">
         <f>IF($A28="","",VLOOKUP($A28,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士説明</v>
       </c>
-      <c r="H28" t="str">
+      <c r="I28" t="str">
         <f>IF($A28="","",VLOOKUP($A28,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士説明</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -2399,18 +2443,19 @@
         <f>IF($A29="","",VLOOKUP($A29,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29"/>
       <c r="E29" s="5"/>
-      <c r="F29" t="str">
+      <c r="F29" s="5"/>
+      <c r="G29" t="str">
         <f>IF($A29="","",VLOOKUP($A29,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面必要</v>
       </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
         <f>IF($A29="","",VLOOKUP($A29,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面必要</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -2422,18 +2467,19 @@
         <f>IF($A30="","",VLOOKUP($A30,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30"/>
       <c r="E30" s="5"/>
-      <c r="F30" t="str">
+      <c r="F30" s="5"/>
+      <c r="G30" t="str">
         <f>IF($A30="","",VLOOKUP($A30,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
         <f>IF($A30="","",VLOOKUP($A30,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -2445,18 +2491,19 @@
         <f>IF($A31="","",VLOOKUP($A31,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D31" s="5"/>
+      <c r="D31"/>
       <c r="E31" s="5"/>
-      <c r="F31" t="str">
+      <c r="F31" s="5"/>
+      <c r="G31" t="str">
         <f>IF($A31="","",VLOOKUP($A31,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定条件で可能</v>
       </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
         <f>IF($A31="","",VLOOKUP($A31,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定条件で可能</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -2468,18 +2515,19 @@
         <f>IF($A32="","",VLOOKUP($A32,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D32" s="5"/>
+      <c r="D32"/>
       <c r="E32" s="5"/>
-      <c r="F32" t="str">
+      <c r="F32" s="5"/>
+      <c r="G32" t="str">
         <f>IF($A32="","",VLOOKUP($A32,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約成立後</v>
       </c>
-      <c r="H32" t="str">
+      <c r="I32" t="str">
         <f>IF($A32="","",VLOOKUP($A32,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約成立後</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -2491,18 +2539,19 @@
         <f>IF($A33="","",VLOOKUP($A33,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33"/>
       <c r="E33" s="5"/>
-      <c r="F33" t="str">
+      <c r="F33" s="5"/>
+      <c r="G33" t="str">
         <f>IF($A33="","",VLOOKUP($A33,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明不要</v>
       </c>
-      <c r="H33" t="str">
+      <c r="I33" t="str">
         <f>IF($A33="","",VLOOKUP($A33,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明不要</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -2514,18 +2563,19 @@
         <f>IF($A34="","",VLOOKUP($A34,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D34" s="5"/>
+      <c r="D34"/>
       <c r="E34" s="5"/>
-      <c r="F34" t="str">
+      <c r="F34" s="5"/>
+      <c r="G34" t="str">
         <f>IF($A34="","",VLOOKUP($A34,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
-      <c r="H34" t="str">
+      <c r="I34" t="str">
         <f>IF($A34="","",VLOOKUP($A34,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>92</v>
       </c>
@@ -2537,18 +2587,19 @@
         <f>IF($A35="","",VLOOKUP($A35,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D35" s="5"/>
+      <c r="D35"/>
       <c r="E35" s="5"/>
-      <c r="F35" t="str">
+      <c r="F35" s="5"/>
+      <c r="G35" t="str">
         <f>IF($A35="","",VLOOKUP($A35,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約後</v>
       </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <f>IF($A35="","",VLOOKUP($A35,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約後</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -2560,18 +2611,19 @@
         <f>IF($A36="","",VLOOKUP($A36,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D36" s="5"/>
+      <c r="D36"/>
       <c r="E36" s="5"/>
-      <c r="F36" t="str">
+      <c r="F36" s="5"/>
+      <c r="G36" t="str">
         <f>IF($A36="","",VLOOKUP($A36,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
-      <c r="H36" t="str">
+      <c r="I36" t="str">
         <f>IF($A36="","",VLOOKUP($A36,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -2583,18 +2635,19 @@
         <f>IF($A37="","",VLOOKUP($A37,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D37" s="5"/>
+      <c r="D37"/>
       <c r="E37" s="5"/>
-      <c r="F37" t="str">
+      <c r="F37" s="5"/>
+      <c r="G37" t="str">
         <f>IF($A37="","",VLOOKUP($A37,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
       </c>
-      <c r="H37" t="str">
+      <c r="I37" t="str">
         <f>IF($A37="","",VLOOKUP($A37,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -2606,18 +2659,19 @@
         <f>IF($A38="","",VLOOKUP($A38,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D38" s="5"/>
+      <c r="D38"/>
       <c r="E38" s="5"/>
-      <c r="F38" t="str">
+      <c r="F38" s="5"/>
+      <c r="G38" t="str">
         <f>IF($A38="","",VLOOKUP($A38,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
-      <c r="H38" t="str">
+      <c r="I38" t="str">
         <f>IF($A38="","",VLOOKUP($A38,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -2629,18 +2683,19 @@
         <f>IF($A39="","",VLOOKUP($A39,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D39" s="5"/>
+      <c r="D39"/>
       <c r="E39" s="5"/>
-      <c r="F39" t="str">
+      <c r="F39" s="5"/>
+      <c r="G39" t="str">
         <f>IF($A39="","",VLOOKUP($A39,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
-      <c r="H39" t="str">
+      <c r="I39" t="str">
         <f>IF($A39="","",VLOOKUP($A39,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>97</v>
       </c>
@@ -2652,18 +2707,19 @@
         <f>IF($A40="","",VLOOKUP($A40,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D40" s="5"/>
+      <c r="D40"/>
       <c r="E40" s="5"/>
-      <c r="F40" t="str">
+      <c r="F40" s="5"/>
+      <c r="G40" t="str">
         <f>IF($A40="","",VLOOKUP($A40,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
       </c>
-      <c r="H40" t="str">
+      <c r="I40" t="str">
         <f>IF($A40="","",VLOOKUP($A40,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>98</v>
       </c>
@@ -2675,18 +2731,19 @@
         <f>IF($A41="","",VLOOKUP($A41,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D41" s="5"/>
+      <c r="D41"/>
       <c r="E41" s="5"/>
-      <c r="F41" t="str">
+      <c r="F41" s="5"/>
+      <c r="G41" t="str">
         <f>IF($A41="","",VLOOKUP($A41,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
-      <c r="H41" t="str">
+      <c r="I41" t="str">
         <f>IF($A41="","",VLOOKUP($A41,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>99</v>
       </c>
@@ -2698,18 +2755,19 @@
         <f>IF($A42="","",VLOOKUP($A42,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D42" s="5"/>
+      <c r="D42"/>
       <c r="E42" s="5"/>
-      <c r="F42" t="str">
+      <c r="F42" s="5"/>
+      <c r="G42" t="str">
         <f>IF($A42="","",VLOOKUP($A42,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
       </c>
-      <c r="H42" t="str">
+      <c r="I42" t="str">
         <f>IF($A42="","",VLOOKUP($A42,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>101</v>
       </c>
@@ -2721,18 +2779,19 @@
         <f>IF($A43="","",VLOOKUP($A43,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D43" s="5"/>
+      <c r="D43"/>
       <c r="E43" s="5"/>
-      <c r="F43" t="str">
+      <c r="F43" s="5"/>
+      <c r="G43" t="str">
         <f>IF($A43="","",VLOOKUP($A43,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
-      <c r="H43" t="str">
+      <c r="I43" t="str">
         <f>IF($A43="","",VLOOKUP($A43,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -2744,18 +2803,19 @@
         <f>IF($A44="","",VLOOKUP($A44,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D44" s="5"/>
+      <c r="D44"/>
       <c r="E44" s="5"/>
-      <c r="F44" t="str">
+      <c r="F44" s="5"/>
+      <c r="G44" t="str">
         <f>IF($A44="","",VLOOKUP($A44,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
-      <c r="H44" t="str">
+      <c r="I44" t="str">
         <f>IF($A44="","",VLOOKUP($A44,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>103</v>
       </c>
@@ -2767,18 +2827,19 @@
         <f>IF($A45="","",VLOOKUP($A45,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D45" s="5"/>
+      <c r="D45"/>
       <c r="E45" s="5"/>
-      <c r="F45" t="str">
+      <c r="F45" s="5"/>
+      <c r="G45" t="str">
         <f>IF($A45="","",VLOOKUP($A45,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H45" t="str">
+      <c r="I45" t="str">
         <f>IF($A45="","",VLOOKUP($A45,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>104</v>
       </c>
@@ -2790,18 +2851,19 @@
         <f>IF($A46="","",VLOOKUP($A46,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D46" s="5"/>
+      <c r="D46"/>
       <c r="E46" s="5"/>
-      <c r="F46" t="str">
+      <c r="F46" s="5"/>
+      <c r="G46" t="str">
         <f>IF($A46="","",VLOOKUP($A46,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H46" t="str">
+      <c r="I46" t="str">
         <f>IF($A46="","",VLOOKUP($A46,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2813,18 +2875,19 @@
         <f>IF($A47="","",VLOOKUP($A47,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D47" s="5"/>
+      <c r="D47"/>
       <c r="E47" s="5"/>
-      <c r="F47" t="str">
+      <c r="F47" s="5"/>
+      <c r="G47" t="str">
         <f>IF($A47="","",VLOOKUP($A47,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>20％以内</v>
       </c>
-      <c r="H47" t="str">
+      <c r="I47" t="str">
         <f>IF($A47="","",VLOOKUP($A47,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>20％以内</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>106</v>
       </c>
@@ -2836,18 +2899,19 @@
         <f>IF($A48="","",VLOOKUP($A48,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D48" s="5"/>
+      <c r="D48"/>
       <c r="E48" s="5"/>
-      <c r="F48" t="str">
+      <c r="F48" s="5"/>
+      <c r="G48" t="str">
         <f>IF($A48="","",VLOOKUP($A48,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H48" t="str">
+      <c r="I48" t="str">
         <f>IF($A48="","",VLOOKUP($A48,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>107</v>
       </c>
@@ -2859,18 +2923,19 @@
         <f>IF($A49="","",VLOOKUP($A49,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D49" s="5"/>
+      <c r="D49"/>
       <c r="E49" s="5"/>
-      <c r="F49" t="str">
+      <c r="F49" s="5"/>
+      <c r="G49" t="str">
         <f>IF($A49="","",VLOOKUP($A49,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>以内</v>
       </c>
-      <c r="H49" t="str">
+      <c r="I49" t="str">
         <f>IF($A49="","",VLOOKUP($A49,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>以内</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>108</v>
       </c>
@@ -2882,18 +2947,19 @@
         <f>IF($A50="","",VLOOKUP($A50,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D50" s="5"/>
+      <c r="D50"/>
       <c r="E50" s="5"/>
-      <c r="F50" t="str">
+      <c r="F50" s="5"/>
+      <c r="G50" t="str">
         <f>IF($A50="","",VLOOKUP($A50,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
-      <c r="H50" t="str">
+      <c r="I50" t="str">
         <f>IF($A50="","",VLOOKUP($A50,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
         <v>109</v>
       </c>
@@ -2905,18 +2971,19 @@
         <f>IF($A51="","",VLOOKUP($A51,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D51" s="5"/>
+      <c r="D51"/>
       <c r="E51" s="5"/>
-      <c r="F51" t="str">
+      <c r="F51" s="5"/>
+      <c r="G51" t="str">
         <f>IF($A51="","",VLOOKUP($A51,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主のみ</v>
       </c>
-      <c r="H51" t="str">
+      <c r="I51" t="str">
         <f>IF($A51="","",VLOOKUP($A51,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主のみ</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -2928,18 +2995,19 @@
         <f>IF($A52="","",VLOOKUP($A52,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D52" s="5"/>
+      <c r="D52"/>
       <c r="E52" s="5"/>
-      <c r="F52" t="str">
+      <c r="F52" s="5"/>
+      <c r="G52" t="str">
         <f>IF($A52="","",VLOOKUP($A52,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
-      <c r="H52" t="str">
+      <c r="I52" t="str">
         <f>IF($A52="","",VLOOKUP($A52,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -2951,18 +3019,19 @@
         <f>IF($A53="","",VLOOKUP($A53,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D53" s="5"/>
+      <c r="D53"/>
       <c r="E53" s="5"/>
-      <c r="F53" t="str">
+      <c r="F53" s="5"/>
+      <c r="G53" t="str">
         <f>IF($A53="","",VLOOKUP($A53,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
-      <c r="H53" t="str">
+      <c r="I53" t="str">
         <f>IF($A53="","",VLOOKUP($A53,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>113</v>
       </c>
@@ -2974,18 +3043,19 @@
         <f>IF($A54="","",VLOOKUP($A54,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D54" s="5"/>
+      <c r="D54"/>
       <c r="E54" s="5"/>
-      <c r="F54" t="str">
+      <c r="F54" s="5"/>
+      <c r="G54" t="str">
         <f>IF($A54="","",VLOOKUP($A54,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>成立時</v>
       </c>
-      <c r="H54" t="str">
+      <c r="I54" t="str">
         <f>IF($A54="","",VLOOKUP($A54,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>成立時</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>114</v>
       </c>
@@ -2997,18 +3067,19 @@
         <f>IF($A55="","",VLOOKUP($A55,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D55" s="5"/>
+      <c r="D55"/>
       <c r="E55" s="5"/>
-      <c r="F55" t="str">
+      <c r="F55" s="5"/>
+      <c r="G55" t="str">
         <f>IF($A55="","",VLOOKUP($A55,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>告示</v>
       </c>
-      <c r="H55" t="str">
+      <c r="I55" t="str">
         <f>IF($A55="","",VLOOKUP($A55,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>告示</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>115</v>
       </c>
@@ -3020,18 +3091,19 @@
         <f>IF($A56="","",VLOOKUP($A56,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D56" s="5"/>
+      <c r="D56"/>
       <c r="E56" s="5"/>
-      <c r="F56" t="str">
+      <c r="F56" s="5"/>
+      <c r="G56" t="str">
         <f>IF($A56="","",VLOOKUP($A56,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>上限あり</v>
       </c>
-      <c r="H56" t="str">
+      <c r="I56" t="str">
         <f>IF($A56="","",VLOOKUP($A56,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>上限あり</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>116</v>
       </c>
@@ -3043,18 +3115,19 @@
         <f>IF($A57="","",VLOOKUP($A57,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D57" s="5"/>
+      <c r="D57"/>
       <c r="E57" s="5"/>
-      <c r="F57" t="str">
+      <c r="F57" s="5"/>
+      <c r="G57" t="str">
         <f>IF($A57="","",VLOOKUP($A57,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H57" t="str">
+      <c r="I57" t="str">
         <f>IF($A57="","",VLOOKUP($A57,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -3066,18 +3139,19 @@
         <f>IF($A58="","",VLOOKUP($A58,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D58" s="5"/>
+      <c r="D58"/>
       <c r="E58" s="5"/>
-      <c r="F58" t="str">
+      <c r="F58" s="5"/>
+      <c r="G58" t="str">
         <f>IF($A58="","",VLOOKUP($A58,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H58" t="str">
+      <c r="I58" t="str">
         <f>IF($A58="","",VLOOKUP($A58,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -3089,18 +3163,19 @@
         <f>IF($A59="","",VLOOKUP($A59,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D59" s="5"/>
+      <c r="D59"/>
       <c r="E59" s="5"/>
-      <c r="F59" t="str">
+      <c r="F59" s="5"/>
+      <c r="G59" t="str">
         <f>IF($A59="","",VLOOKUP($A59,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H59" t="str">
+      <c r="I59" t="str">
         <f>IF($A59="","",VLOOKUP($A59,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
         <v>119</v>
       </c>
@@ -3112,18 +3187,19 @@
         <f>IF($A60="","",VLOOKUP($A60,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D60" s="5"/>
+      <c r="D60"/>
       <c r="E60" s="5"/>
-      <c r="F60" t="str">
+      <c r="F60" s="5"/>
+      <c r="G60" t="str">
         <f>IF($A60="","",VLOOKUP($A60,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>大臣も可</v>
       </c>
-      <c r="H60" t="str">
+      <c r="I60" t="str">
         <f>IF($A60="","",VLOOKUP($A60,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>大臣も可</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -3135,18 +3211,19 @@
         <f>IF($A61="","",VLOOKUP($A61,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D61" s="5"/>
+      <c r="D61"/>
       <c r="E61" s="5"/>
-      <c r="F61" t="str">
+      <c r="F61" s="5"/>
+      <c r="G61" t="str">
         <f>IF($A61="","",VLOOKUP($A61,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H61" t="str">
+      <c r="I61" t="str">
         <f>IF($A61="","",VLOOKUP($A61,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
         <v>121</v>
       </c>
@@ -3158,18 +3235,19 @@
         <f>IF($A62="","",VLOOKUP($A62,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D62" s="5"/>
+      <c r="D62"/>
       <c r="E62" s="5"/>
-      <c r="F62" t="str">
+      <c r="F62" s="5"/>
+      <c r="G62" t="str">
         <f>IF($A62="","",VLOOKUP($A62,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H62" t="str">
+      <c r="I62" t="str">
         <f>IF($A62="","",VLOOKUP($A62,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
         <v>123</v>
       </c>
@@ -3181,18 +3259,19 @@
         <f>IF($A63="","",VLOOKUP($A63,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D63" s="5"/>
+      <c r="D63"/>
       <c r="E63" s="5"/>
-      <c r="F63" t="str">
+      <c r="F63" s="5"/>
+      <c r="G63" t="str">
         <f>IF($A63="","",VLOOKUP($A63,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H63" t="str">
+      <c r="I63" t="str">
         <f>IF($A63="","",VLOOKUP($A63,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -3204,18 +3283,19 @@
         <f>IF($A64="","",VLOOKUP($A64,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D64" s="5"/>
+      <c r="D64"/>
       <c r="E64" s="5"/>
-      <c r="F64" t="str">
+      <c r="F64" s="5"/>
+      <c r="G64" t="str">
         <f>IF($A64="","",VLOOKUP($A64,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H64" t="str">
+      <c r="I64" t="str">
         <f>IF($A64="","",VLOOKUP($A64,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>125</v>
       </c>
@@ -3227,18 +3307,19 @@
         <f>IF($A65="","",VLOOKUP($A65,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D65" s="5"/>
+      <c r="D65"/>
       <c r="E65" s="5"/>
-      <c r="F65" t="str">
+      <c r="F65" s="5"/>
+      <c r="G65" t="str">
         <f>IF($A65="","",VLOOKUP($A65,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H65" t="str">
+      <c r="I65" t="str">
         <f>IF($A65="","",VLOOKUP($A65,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -3250,18 +3331,19 @@
         <f>IF($A66="","",VLOOKUP($A66,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D66" s="5"/>
+      <c r="D66"/>
       <c r="E66" s="5"/>
-      <c r="F66" t="str">
+      <c r="F66" s="5"/>
+      <c r="G66" t="str">
         <f>IF($A66="","",VLOOKUP($A66,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H66" t="str">
+      <c r="I66" t="str">
         <f>IF($A66="","",VLOOKUP($A66,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -3273,18 +3355,19 @@
         <f>IF($A67="","",VLOOKUP($A67,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D67" s="5"/>
+      <c r="D67"/>
       <c r="E67" s="5"/>
-      <c r="F67" t="str">
+      <c r="F67" s="5"/>
+      <c r="G67" t="str">
         <f>IF($A67="","",VLOOKUP($A67,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>提示</v>
       </c>
-      <c r="H67" t="str">
+      <c r="I67" t="str">
         <f>IF($A67="","",VLOOKUP($A67,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>提示</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
         <v>128</v>
       </c>
@@ -3296,18 +3379,19 @@
         <f>IF($A68="","",VLOOKUP($A68,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D68" s="5"/>
+      <c r="D68"/>
       <c r="E68" s="5"/>
-      <c r="F68" t="str">
+      <c r="F68" s="5"/>
+      <c r="G68" t="str">
         <f>IF($A68="","",VLOOKUP($A68,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>携帯</v>
       </c>
-      <c r="H68" t="str">
+      <c r="I68" t="str">
         <f>IF($A68="","",VLOOKUP($A68,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>携帯</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>129</v>
       </c>
@@ -3319,18 +3403,19 @@
         <f>IF($A69="","",VLOOKUP($A69,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D69" s="5"/>
+      <c r="D69"/>
       <c r="E69" s="5"/>
-      <c r="F69" t="str">
+      <c r="F69" s="5"/>
+      <c r="G69" t="str">
         <f>IF($A69="","",VLOOKUP($A69,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H69" t="str">
+      <c r="I69" t="str">
         <f>IF($A69="","",VLOOKUP($A69,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>130</v>
       </c>
@@ -3342,18 +3427,19 @@
         <f>IF($A70="","",VLOOKUP($A70,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D70" s="5"/>
+      <c r="D70"/>
       <c r="E70" s="5"/>
-      <c r="F70" t="str">
+      <c r="F70" s="5"/>
+      <c r="G70" t="str">
         <f>IF($A70="","",VLOOKUP($A70,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
-      <c r="H70" t="str">
+      <c r="I70" t="str">
         <f>IF($A70="","",VLOOKUP($A70,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>131</v>
       </c>
@@ -3365,18 +3451,19 @@
         <f>IF($A71="","",VLOOKUP($A71,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D71" s="5"/>
+      <c r="D71"/>
       <c r="E71" s="5"/>
-      <c r="F71" t="str">
+      <c r="F71" s="5"/>
+      <c r="G71" t="str">
         <f>IF($A71="","",VLOOKUP($A71,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H71" t="str">
+      <c r="I71" t="str">
         <f>IF($A71="","",VLOOKUP($A71,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>132</v>
       </c>
@@ -3388,18 +3475,19 @@
         <f>IF($A72="","",VLOOKUP($A72,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D72" s="5"/>
+      <c r="D72"/>
       <c r="E72" s="5"/>
-      <c r="F72" t="str">
+      <c r="F72" s="5"/>
+      <c r="G72" t="str">
         <f>IF($A72="","",VLOOKUP($A72,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
-      <c r="H72" t="str">
+      <c r="I72" t="str">
         <f>IF($A72="","",VLOOKUP($A72,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>134</v>
       </c>
@@ -3411,18 +3499,19 @@
         <f>IF($A73="","",VLOOKUP($A73,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D73" s="5"/>
+      <c r="D73"/>
       <c r="E73" s="5"/>
-      <c r="F73" t="str">
+      <c r="F73" s="5"/>
+      <c r="G73" t="str">
         <f>IF($A73="","",VLOOKUP($A73,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
-      <c r="H73" t="str">
+      <c r="I73" t="str">
         <f>IF($A73="","",VLOOKUP($A73,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>135</v>
       </c>
@@ -3434,18 +3523,19 @@
         <f>IF($A74="","",VLOOKUP($A74,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D74" s="5"/>
+      <c r="D74"/>
       <c r="E74" s="5"/>
-      <c r="F74" t="str">
+      <c r="F74" s="5"/>
+      <c r="G74" t="str">
         <f>IF($A74="","",VLOOKUP($A74,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H74" t="str">
+      <c r="I74" t="str">
         <f>IF($A74="","",VLOOKUP($A74,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>136</v>
       </c>
@@ -3457,18 +3547,19 @@
         <f>IF($A75="","",VLOOKUP($A75,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D75" s="5"/>
+      <c r="D75"/>
       <c r="E75" s="5"/>
-      <c r="F75" t="str">
+      <c r="F75" s="5"/>
+      <c r="G75" t="str">
         <f>IF($A75="","",VLOOKUP($A75,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
       </c>
-      <c r="H75" t="str">
+      <c r="I75" t="str">
         <f>IF($A75="","",VLOOKUP($A75,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>137</v>
       </c>
@@ -3480,18 +3571,19 @@
         <f>IF($A76="","",VLOOKUP($A76,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D76" s="5"/>
+      <c r="D76"/>
       <c r="E76" s="5"/>
-      <c r="F76" t="str">
+      <c r="F76" s="5"/>
+      <c r="G76" t="str">
         <f>IF($A76="","",VLOOKUP($A76,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>別</v>
       </c>
-      <c r="H76" t="str">
+      <c r="I76" t="str">
         <f>IF($A76="","",VLOOKUP($A76,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>別</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>138</v>
       </c>
@@ -3503,18 +3595,19 @@
         <f>IF($A77="","",VLOOKUP($A77,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D77" s="5"/>
+      <c r="D77"/>
       <c r="E77" s="5"/>
-      <c r="F77" t="str">
+      <c r="F77" s="5"/>
+      <c r="G77" t="str">
         <f>IF($A77="","",VLOOKUP($A77,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H77" t="str">
+      <c r="I77" t="str">
         <f>IF($A77="","",VLOOKUP($A77,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
         <v>139</v>
       </c>
@@ -3526,18 +3619,19 @@
         <f>IF($A78="","",VLOOKUP($A78,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D78" s="5"/>
+      <c r="D78"/>
       <c r="E78" s="5"/>
-      <c r="F78" t="str">
+      <c r="F78" s="5"/>
+      <c r="G78" t="str">
         <f>IF($A78="","",VLOOKUP($A78,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H78" t="str">
+      <c r="I78" t="str">
         <f>IF($A78="","",VLOOKUP($A78,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
         <v>140</v>
       </c>
@@ -3549,18 +3643,19 @@
         <f>IF($A79="","",VLOOKUP($A79,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D79" s="5"/>
+      <c r="D79"/>
       <c r="E79" s="5"/>
-      <c r="F79" t="str">
+      <c r="F79" s="5"/>
+      <c r="G79" t="str">
         <f>IF($A79="","",VLOOKUP($A79,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H79" t="str">
+      <c r="I79" t="str">
         <f>IF($A79="","",VLOOKUP($A79,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
         <v>141</v>
       </c>
@@ -3572,18 +3667,19 @@
         <f>IF($A80="","",VLOOKUP($A80,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D80" s="5"/>
+      <c r="D80"/>
       <c r="E80" s="5"/>
-      <c r="F80" t="str">
+      <c r="F80" s="5"/>
+      <c r="G80" t="str">
         <f>IF($A80="","",VLOOKUP($A80,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
-      <c r="H80" t="str">
+      <c r="I80" t="str">
         <f>IF($A80="","",VLOOKUP($A80,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
         <v>142</v>
       </c>
@@ -3595,18 +3691,19 @@
         <f>IF($A81="","",VLOOKUP($A81,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D81" s="5"/>
+      <c r="D81"/>
       <c r="E81" s="5"/>
-      <c r="F81" t="str">
+      <c r="F81" s="5"/>
+      <c r="G81" t="str">
         <f>IF($A81="","",VLOOKUP($A81,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
-      <c r="H81" t="str">
+      <c r="I81" t="str">
         <f>IF($A81="","",VLOOKUP($A81,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
         <v>143</v>
       </c>
@@ -3618,18 +3715,19 @@
         <f>IF($A82="","",VLOOKUP($A82,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D82" s="5"/>
+      <c r="D82"/>
       <c r="E82" s="5"/>
-      <c r="F82" t="str">
+      <c r="F82" s="5"/>
+      <c r="G82" t="str">
         <f>IF($A82="","",VLOOKUP($A82,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者は免許を受ける前に広告を出してはならない</v>
       </c>
-      <c r="H82" t="str">
+      <c r="I82" t="str">
         <f>IF($A82="","",VLOOKUP($A82,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者は免許を受ける前に広告を出してはならない</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
         <v>145</v>
       </c>
@@ -3641,18 +3739,19 @@
         <f>IF($A83="","",VLOOKUP($A83,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D83" s="5"/>
+      <c r="D83"/>
       <c r="E83" s="5"/>
-      <c r="F83" t="str">
+      <c r="F83" s="5"/>
+      <c r="G83" t="str">
         <f>IF($A83="","",VLOOKUP($A83,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売主・代理・媒介など取引態様の明示が必要</v>
       </c>
-      <c r="H83" t="str">
+      <c r="I83" t="str">
         <f>IF($A83="","",VLOOKUP($A83,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売主・代理・媒介など取引態様の明示が必要</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
         <v>146</v>
       </c>
@@ -3664,18 +3763,19 @@
         <f>IF($A84="","",VLOOKUP($A84,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D84" s="5"/>
+      <c r="D84"/>
       <c r="E84" s="5"/>
-      <c r="F84" t="str">
+      <c r="F84" s="5"/>
+      <c r="G84" t="str">
         <f>IF($A84="","",VLOOKUP($A84,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>著しく事実に相違する広告は禁止されている</v>
       </c>
-      <c r="H84" t="str">
+      <c r="I84" t="str">
         <f>IF($A84="","",VLOOKUP($A84,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>著しく事実に相違する広告は禁止されている</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
         <v>147</v>
       </c>
@@ -3687,18 +3787,19 @@
         <f>IF($A85="","",VLOOKUP($A85,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D85" s="5"/>
+      <c r="D85"/>
       <c r="E85" s="5"/>
-      <c r="F85" t="str">
+      <c r="F85" s="5"/>
+      <c r="G85" t="str">
         <f>IF($A85="","",VLOOKUP($A85,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>造成工事完了前の広告には制限がある</v>
       </c>
-      <c r="H85" t="str">
+      <c r="I85" t="str">
         <f>IF($A85="","",VLOOKUP($A85,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>造成工事完了前の広告には制限がある</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
         <v>148</v>
       </c>
@@ -3710,18 +3811,19 @@
         <f>IF($A86="","",VLOOKUP($A86,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D86" s="5"/>
+      <c r="D86"/>
       <c r="E86" s="5"/>
-      <c r="F86" t="str">
+      <c r="F86" s="5"/>
+      <c r="G86" t="str">
         <f>IF($A86="","",VLOOKUP($A86,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>許可番号などの表示が必要</v>
       </c>
-      <c r="H86" t="str">
+      <c r="I86" t="str">
         <f>IF($A86="","",VLOOKUP($A86,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>許可番号などの表示が必要</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
         <v>149</v>
       </c>
@@ -3733,18 +3835,19 @@
         <f>IF($A87="","",VLOOKUP($A87,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D87" s="5"/>
+      <c r="D87"/>
       <c r="E87" s="5"/>
-      <c r="F87" t="str">
+      <c r="F87" s="5"/>
+      <c r="G87" t="str">
         <f>IF($A87="","",VLOOKUP($A87,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介、専任媒介、専属専任媒介</v>
       </c>
-      <c r="H87" t="str">
+      <c r="I87" t="str">
         <f>IF($A87="","",VLOOKUP($A87,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介、専任媒介、専属専任媒介</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
         <v>150</v>
       </c>
@@ -3756,18 +3859,19 @@
         <f>IF($A88="","",VLOOKUP($A88,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D88" s="5"/>
+      <c r="D88"/>
       <c r="E88" s="5"/>
-      <c r="F88" t="str">
+      <c r="F88" s="5"/>
+      <c r="G88" t="str">
         <f>IF($A88="","",VLOOKUP($A88,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専属専任媒介では自己発見取引は禁止</v>
       </c>
-      <c r="H88" t="str">
+      <c r="I88" t="str">
         <f>IF($A88="","",VLOOKUP($A88,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専属専任媒介では自己発見取引は禁止</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
         <v>151</v>
       </c>
@@ -3779,18 +3883,19 @@
         <f>IF($A89="","",VLOOKUP($A89,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D89" s="5"/>
+      <c r="D89"/>
       <c r="E89" s="5"/>
-      <c r="F89" t="str">
+      <c r="F89" s="5"/>
+      <c r="G89" t="str">
         <f>IF($A89="","",VLOOKUP($A89,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介では自己発見取引は可能</v>
       </c>
-      <c r="H89" t="str">
+      <c r="I89" t="str">
         <f>IF($A89="","",VLOOKUP($A89,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介では自己発見取引は可能</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
         <v>152</v>
       </c>
@@ -3802,18 +3907,19 @@
         <f>IF($A90="","",VLOOKUP($A90,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D90" s="5"/>
+      <c r="D90"/>
       <c r="E90" s="5"/>
-      <c r="F90" t="str">
+      <c r="F90" s="5"/>
+      <c r="G90" t="str">
         <f>IF($A90="","",VLOOKUP($A90,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約は書面交付が必要</v>
       </c>
-      <c r="H90" t="str">
+      <c r="I90" t="str">
         <f>IF($A90="","",VLOOKUP($A90,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約は書面交付が必要</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
         <v>153</v>
       </c>
@@ -3825,18 +3931,19 @@
         <f>IF($A91="","",VLOOKUP($A91,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D91" s="5"/>
+      <c r="D91"/>
       <c r="E91" s="5"/>
-      <c r="F91" t="str">
+      <c r="F91" s="5"/>
+      <c r="G91" t="str">
         <f>IF($A91="","",VLOOKUP($A91,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約の期間は3か月以内</v>
       </c>
-      <c r="H91" t="str">
+      <c r="I91" t="str">
         <f>IF($A91="","",VLOOKUP($A91,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約の期間は3か月以内</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
         <v>154</v>
       </c>
@@ -3848,18 +3955,19 @@
         <f>IF($A92="","",VLOOKUP($A92,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D92" s="5"/>
+      <c r="D92"/>
       <c r="E92" s="5"/>
-      <c r="F92" t="str">
+      <c r="F92" s="5"/>
+      <c r="G92" t="str">
         <f>IF($A92="","",VLOOKUP($A92,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業務処理状況の報告義務あり</v>
       </c>
-      <c r="H92" t="str">
+      <c r="I92" t="str">
         <f>IF($A92="","",VLOOKUP($A92,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業務処理状況の報告義務あり</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
         <v>156</v>
       </c>
@@ -3871,18 +3979,19 @@
         <f>IF($A93="","",VLOOKUP($A93,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D93" s="5"/>
+      <c r="D93"/>
       <c r="E93" s="5"/>
-      <c r="F93" t="str">
+      <c r="F93" s="5"/>
+      <c r="G93" t="str">
         <f>IF($A93="","",VLOOKUP($A93,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介は2週間に1回以上</v>
       </c>
-      <c r="H93" t="str">
+      <c r="I93" t="str">
         <f>IF($A93="","",VLOOKUP($A93,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介は2週間に1回以上</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
         <v>157</v>
       </c>
@@ -3894,18 +4003,19 @@
         <f>IF($A94="","",VLOOKUP($A94,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D94" s="5"/>
+      <c r="D94"/>
       <c r="E94" s="5"/>
-      <c r="F94" t="str">
+      <c r="F94" s="5"/>
+      <c r="G94" t="str">
         <f>IF($A94="","",VLOOKUP($A94,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介には報告義務はない</v>
       </c>
-      <c r="H94" t="str">
+      <c r="I94" t="str">
         <f>IF($A94="","",VLOOKUP($A94,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介には報告義務はない</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
         <v>158</v>
       </c>
@@ -3917,18 +4027,19 @@
         <f>IF($A95="","",VLOOKUP($A95,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D95" s="5"/>
+      <c r="D95"/>
       <c r="E95" s="5"/>
-      <c r="F95" t="str">
+      <c r="F95" s="5"/>
+      <c r="G95" t="str">
         <f>IF($A95="","",VLOOKUP($A95,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後5日以内に登録</v>
       </c>
-      <c r="H95" t="str">
+      <c r="I95" t="str">
         <f>IF($A95="","",VLOOKUP($A95,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後5日以内に登録</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
         <v>159</v>
       </c>
@@ -3940,18 +4051,19 @@
         <f>IF($A96="","",VLOOKUP($A96,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D96" s="5"/>
+      <c r="D96"/>
       <c r="E96" s="5"/>
-      <c r="F96" t="str">
+      <c r="F96" s="5"/>
+      <c r="G96" t="str">
         <f>IF($A96="","",VLOOKUP($A96,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後7日以内に登録</v>
       </c>
-      <c r="H96" t="str">
+      <c r="I96" t="str">
         <f>IF($A96="","",VLOOKUP($A96,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後7日以内に登録</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
         <v>160</v>
       </c>
@@ -3963,18 +4075,19 @@
         <f>IF($A97="","",VLOOKUP($A97,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D97" s="5"/>
+      <c r="D97"/>
       <c r="E97" s="5"/>
-      <c r="F97" t="str">
+      <c r="F97" s="5"/>
+      <c r="G97" t="str">
         <f>IF($A97="","",VLOOKUP($A97,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付金等は代金の20%以内</v>
       </c>
-      <c r="H97" t="str">
+      <c r="I97" t="str">
         <f>IF($A97="","",VLOOKUP($A97,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付金等は代金の20%以内</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
         <v>161</v>
       </c>
@@ -3986,18 +4099,19 @@
         <f>IF($A98="","",VLOOKUP($A98,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D98" s="5"/>
+      <c r="D98"/>
       <c r="E98" s="5"/>
-      <c r="F98" t="str">
+      <c r="F98" s="5"/>
+      <c r="G98" t="str">
         <f>IF($A98="","",VLOOKUP($A98,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>特約がなければ解約手付</v>
       </c>
-      <c r="H98" t="str">
+      <c r="I98" t="str">
         <f>IF($A98="","",VLOOKUP($A98,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>特約がなければ解約手付</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
         <v>162</v>
       </c>
@@ -4009,18 +4123,19 @@
         <f>IF($A99="","",VLOOKUP($A99,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D99" s="5"/>
+      <c r="D99"/>
       <c r="E99" s="5"/>
-      <c r="F99" t="str">
+      <c r="F99" s="5"/>
+      <c r="G99" t="str">
         <f>IF($A99="","",VLOOKUP($A99,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>解約手付の原則</v>
       </c>
-      <c r="H99" t="str">
+      <c r="I99" t="str">
         <f>IF($A99="","",VLOOKUP($A99,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>解約手付の原則</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
         <v>163</v>
       </c>
@@ -4032,18 +4147,19 @@
         <f>IF($A100="","",VLOOKUP($A100,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D100" s="5"/>
+      <c r="D100"/>
       <c r="E100" s="5"/>
-      <c r="F100" t="str">
+      <c r="F100" s="5"/>
+      <c r="G100" t="str">
         <f>IF($A100="","",VLOOKUP($A100,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付倍返し</v>
       </c>
-      <c r="H100" t="str">
+      <c r="I100" t="str">
         <f>IF($A100="","",VLOOKUP($A100,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付倍返し</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
         <v>164</v>
       </c>
@@ -4055,18 +4171,19 @@
         <f>IF($A101="","",VLOOKUP($A101,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D101" s="5"/>
+      <c r="D101"/>
       <c r="E101" s="5"/>
-      <c r="F101" t="str">
+      <c r="F101" s="5"/>
+      <c r="G101" t="str">
         <f>IF($A101="","",VLOOKUP($A101,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>履行着手後は解除不可</v>
       </c>
-      <c r="H101" t="str">
+      <c r="I101" t="str">
         <f>IF($A101="","",VLOOKUP($A101,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>履行着手後は解除不可</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
         <v>165</v>
       </c>
@@ -4078,18 +4195,19 @@
         <f>IF($A102="","",VLOOKUP($A102,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D102" s="5"/>
+      <c r="D102"/>
       <c r="E102" s="5"/>
-      <c r="F102" t="str">
+      <c r="F102" s="5"/>
+      <c r="G102" t="str">
         <f>IF($A102="","",VLOOKUP($A102,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定の場合クーリングオフ可能</v>
       </c>
-      <c r="H102" t="str">
+      <c r="I102" t="str">
         <f>IF($A102="","",VLOOKUP($A102,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定の場合クーリングオフ可能</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
         <v>167</v>
       </c>
@@ -4101,18 +4219,19 @@
         <f>IF($A103="","",VLOOKUP($A103,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D103" s="5"/>
+      <c r="D103"/>
       <c r="E103" s="5"/>
-      <c r="F103" t="str">
+      <c r="F103" s="5"/>
+      <c r="G103" t="str">
         <f>IF($A103="","",VLOOKUP($A103,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>事務所契約は対象外</v>
       </c>
-      <c r="H103" t="str">
+      <c r="I103" t="str">
         <f>IF($A103="","",VLOOKUP($A103,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>事務所契約は対象外</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
         <v>168</v>
       </c>
@@ -4124,18 +4243,19 @@
         <f>IF($A104="","",VLOOKUP($A104,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D104" s="5"/>
+      <c r="D104"/>
       <c r="E104" s="5"/>
-      <c r="F104" t="str">
+      <c r="F104" s="5"/>
+      <c r="G104" t="str">
         <f>IF($A104="","",VLOOKUP($A104,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面受領から8日</v>
       </c>
-      <c r="H104" t="str">
+      <c r="I104" t="str">
         <f>IF($A104="","",VLOOKUP($A104,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面受領から8日</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
         <v>169</v>
       </c>
@@ -4147,18 +4267,19 @@
         <f>IF($A105="","",VLOOKUP($A105,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D105" s="5"/>
+      <c r="D105"/>
       <c r="E105" s="5"/>
-      <c r="F105" t="str">
+      <c r="F105" s="5"/>
+      <c r="G105" t="str">
         <f>IF($A105="","",VLOOKUP($A105,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面通知が必要</v>
       </c>
-      <c r="H105" t="str">
+      <c r="I105" t="str">
         <f>IF($A105="","",VLOOKUP($A105,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面通知が必要</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
         <v>170</v>
       </c>
@@ -4170,18 +4291,19 @@
         <f>IF($A106="","",VLOOKUP($A106,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D106" s="5"/>
+      <c r="D106"/>
       <c r="E106" s="5"/>
-      <c r="F106" t="str">
+      <c r="F106" s="5"/>
+      <c r="G106" t="str">
         <f>IF($A106="","",VLOOKUP($A106,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>損害賠償請求不可</v>
       </c>
-      <c r="H106" t="str">
+      <c r="I106" t="str">
         <f>IF($A106="","",VLOOKUP($A106,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>損害賠償請求不可</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
         <v>171</v>
       </c>
@@ -4193,18 +4315,19 @@
         <f>IF($A107="","",VLOOKUP($A107,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D107" s="5"/>
+      <c r="D107"/>
       <c r="E107" s="5"/>
-      <c r="F107" t="str">
+      <c r="F107" s="5"/>
+      <c r="G107" t="str">
         <f>IF($A107="","",VLOOKUP($A107,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金の20%以内</v>
       </c>
-      <c r="H107" t="str">
+      <c r="I107" t="str">
         <f>IF($A107="","",VLOOKUP($A107,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金の20%以内</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
         <v>172</v>
       </c>
@@ -4216,18 +4339,19 @@
         <f>IF($A108="","",VLOOKUP($A108,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D108" s="5"/>
+      <c r="D108"/>
       <c r="E108" s="5"/>
-      <c r="F108" t="str">
+      <c r="F108" s="5"/>
+      <c r="G108" t="str">
         <f>IF($A108="","",VLOOKUP($A108,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>合算して20%以内</v>
       </c>
-      <c r="H108" t="str">
+      <c r="I108" t="str">
         <f>IF($A108="","",VLOOKUP($A108,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>合算して20%以内</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
         <v>173</v>
       </c>
@@ -4239,18 +4363,19 @@
         <f>IF($A109="","",VLOOKUP($A109,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D109" s="5"/>
+      <c r="D109"/>
       <c r="E109" s="5"/>
-      <c r="F109" t="str">
+      <c r="F109" s="5"/>
+      <c r="G109" t="str">
         <f>IF($A109="","",VLOOKUP($A109,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>超過部分は無効</v>
       </c>
-      <c r="H109" t="str">
+      <c r="I109" t="str">
         <f>IF($A109="","",VLOOKUP($A109,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>超過部分は無効</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
         <v>174</v>
       </c>
@@ -4262,18 +4387,19 @@
         <f>IF($A110="","",VLOOKUP($A110,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D110" s="5"/>
+      <c r="D110"/>
       <c r="E110" s="5"/>
-      <c r="F110" t="str">
+      <c r="F110" s="5"/>
+      <c r="G110" t="str">
         <f>IF($A110="","",VLOOKUP($A110,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>2年以上</v>
       </c>
-      <c r="H110" t="str">
+      <c r="I110" t="str">
         <f>IF($A110="","",VLOOKUP($A110,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>2年以上</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
         <v>175</v>
       </c>
@@ -4285,18 +4411,19 @@
         <f>IF($A111="","",VLOOKUP($A111,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D111" s="5"/>
+      <c r="D111"/>
       <c r="E111" s="5"/>
-      <c r="F111" t="str">
+      <c r="F111" s="5"/>
+      <c r="G111" t="str">
         <f>IF($A111="","",VLOOKUP($A111,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主の場合不可</v>
       </c>
-      <c r="H111" t="str">
+      <c r="I111" t="str">
         <f>IF($A111="","",VLOOKUP($A111,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主の場合不可</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
         <v>176</v>
       </c>
@@ -4308,18 +4435,19 @@
         <f>IF($A112="","",VLOOKUP($A112,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D112" s="5"/>
+      <c r="D112"/>
       <c r="E112" s="5"/>
-      <c r="F112" t="str">
+      <c r="F112" s="5"/>
+      <c r="G112" t="str">
         <f>IF($A112="","",VLOOKUP($A112,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金完済まで留保</v>
       </c>
-      <c r="H112" t="str">
+      <c r="I112" t="str">
         <f>IF($A112="","",VLOOKUP($A112,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金完済まで留保</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
         <v>178</v>
       </c>
@@ -4331,18 +4459,19 @@
         <f>IF($A113="","",VLOOKUP($A113,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D113" s="5"/>
+      <c r="D113"/>
       <c r="E113" s="5"/>
-      <c r="F113" t="str">
+      <c r="F113" s="5"/>
+      <c r="G113" t="str">
         <f>IF($A113="","",VLOOKUP($A113,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間の催告が必要</v>
       </c>
-      <c r="H113" t="str">
+      <c r="I113" t="str">
         <f>IF($A113="","",VLOOKUP($A113,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間の催告が必要</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
         <v>179</v>
       </c>
@@ -4354,18 +4483,19 @@
         <f>IF($A114="","",VLOOKUP($A114,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D114" s="5"/>
+      <c r="D114"/>
       <c r="E114" s="5"/>
-      <c r="F114" t="str">
+      <c r="F114" s="5"/>
+      <c r="G114" t="str">
         <f>IF($A114="","",VLOOKUP($A114,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>30日以上</v>
       </c>
-      <c r="H114" t="str">
+      <c r="I114" t="str">
         <f>IF($A114="","",VLOOKUP($A114,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>30日以上</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
         <v>180</v>
       </c>
@@ -4377,18 +4507,19 @@
         <f>IF($A115="","",VLOOKUP($A115,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D115" s="5"/>
+      <c r="D115"/>
       <c r="E115" s="5"/>
-      <c r="F115" t="str">
+      <c r="F115" s="5"/>
+      <c r="G115" t="str">
         <f>IF($A115="","",VLOOKUP($A115,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>催告必要</v>
       </c>
-      <c r="H115" t="str">
+      <c r="I115" t="str">
         <f>IF($A115="","",VLOOKUP($A115,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>催告必要</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
         <v>181</v>
       </c>
@@ -4400,18 +4531,19 @@
         <f>IF($A116="","",VLOOKUP($A116,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D116" s="5"/>
+      <c r="D116"/>
       <c r="E116" s="5"/>
-      <c r="F116" t="str">
+      <c r="F116" s="5"/>
+      <c r="G116" t="str">
         <f>IF($A116="","",VLOOKUP($A116,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>融資不成立の場合解除</v>
       </c>
-      <c r="H116" t="str">
+      <c r="I116" t="str">
         <f>IF($A116="","",VLOOKUP($A116,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>融資不成立の場合解除</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
         <v>182</v>
       </c>
@@ -4423,18 +4555,19 @@
         <f>IF($A117="","",VLOOKUP($A117,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D117" s="5"/>
+      <c r="D117"/>
       <c r="E117" s="5"/>
-      <c r="F117" t="str">
+      <c r="F117" s="5"/>
+      <c r="G117" t="str">
         <f>IF($A117="","",VLOOKUP($A117,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>民法契約の特約</v>
       </c>
-      <c r="H117" t="str">
+      <c r="I117" t="str">
         <f>IF($A117="","",VLOOKUP($A117,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>民法契約の特約</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
         <v>183</v>
       </c>
@@ -4446,18 +4579,19 @@
         <f>IF($A118="","",VLOOKUP($A118,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D118" s="5"/>
+      <c r="D118"/>
       <c r="E118" s="5"/>
-      <c r="F118" t="str">
+      <c r="F118" s="5"/>
+      <c r="G118" t="str">
         <f>IF($A118="","",VLOOKUP($A118,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>報酬規定あり</v>
       </c>
-      <c r="H118" t="str">
+      <c r="I118" t="str">
         <f>IF($A118="","",VLOOKUP($A118,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>報酬規定あり</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
         <v>184</v>
       </c>
@@ -4469,18 +4603,19 @@
         <f>IF($A119="","",VLOOKUP($A119,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D119" s="5"/>
+      <c r="D119"/>
       <c r="E119" s="5"/>
-      <c r="F119" t="str">
+      <c r="F119" s="5"/>
+      <c r="G119" t="str">
         <f>IF($A119="","",VLOOKUP($A119,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>=+消費税</v>
       </c>
-      <c r="H119" t="str">
+      <c r="I119" t="str">
         <f>IF($A119="","",VLOOKUP($A119,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>=+消費税</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
         <v>185</v>
       </c>
@@ -4492,18 +4627,19 @@
         <f>IF($A120="","",VLOOKUP($A120,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D120" s="5"/>
+      <c r="D120"/>
       <c r="E120" s="5"/>
-      <c r="F120" t="str">
+      <c r="F120" s="5"/>
+      <c r="G120" t="str">
         <f>IF($A120="","",VLOOKUP($A120,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>双方から受領可能</v>
       </c>
-      <c r="H120" t="str">
+      <c r="I120" t="str">
         <f>IF($A120="","",VLOOKUP($A120,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>双方から受領可能</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
         <v>186</v>
       </c>
@@ -4515,18 +4651,19 @@
         <f>IF($A121="","",VLOOKUP($A121,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D121" s="5"/>
+      <c r="D121"/>
       <c r="E121" s="5"/>
-      <c r="F121" t="str">
+      <c r="F121" s="5"/>
+      <c r="G121" t="str">
         <f>IF($A121="","",VLOOKUP($A121,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>国土交通省告示で上限あり</v>
       </c>
-      <c r="H121" t="str">
+      <c r="I121" t="str">
         <f>IF($A121="","",VLOOKUP($A121,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>国土交通省告示で上限あり</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
         <v>187</v>
       </c>
@@ -4538,18 +4675,19 @@
         <f>IF($A122="","",VLOOKUP($A122,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D122" s="5"/>
+      <c r="D122"/>
       <c r="E122" s="5"/>
-      <c r="F122" t="str">
+      <c r="F122" s="5"/>
+      <c r="G122" t="str">
         <f>IF($A122="","",VLOOKUP($A122,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>重大違反の場合</v>
       </c>
-      <c r="H122" t="str">
+      <c r="I122" t="str">
         <f>IF($A122="","",VLOOKUP($A122,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>重大違反の場合</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
         <v>189</v>
       </c>
@@ -4561,18 +4699,19 @@
         <f>IF($A123="","",VLOOKUP($A123,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D123" s="5"/>
+      <c r="D123"/>
       <c r="E123" s="5"/>
-      <c r="F123" t="str">
+      <c r="F123" s="5"/>
+      <c r="G123" t="str">
         <f>IF($A123="","",VLOOKUP($A123,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間営業停止</v>
       </c>
-      <c r="H123" t="str">
+      <c r="I123" t="str">
         <f>IF($A123="","",VLOOKUP($A123,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間営業停止</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
         <v>190</v>
       </c>
@@ -4584,18 +4723,19 @@
         <f>IF($A124="","",VLOOKUP($A124,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D124" s="5"/>
+      <c r="D124"/>
       <c r="E124" s="5"/>
-      <c r="F124" t="str">
+      <c r="F124" s="5"/>
+      <c r="G124" t="str">
         <f>IF($A124="","",VLOOKUP($A124,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>行政指導処分</v>
       </c>
-      <c r="H124" t="str">
+      <c r="I124" t="str">
         <f>IF($A124="","",VLOOKUP($A124,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>行政指導処分</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
         <v>191</v>
       </c>
@@ -4607,18 +4747,19 @@
         <f>IF($A125="","",VLOOKUP($A125,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D125" s="5"/>
+      <c r="D125"/>
       <c r="E125" s="5"/>
-      <c r="F125" t="str">
+      <c r="F125" s="5"/>
+      <c r="G125" t="str">
         <f>IF($A125="","",VLOOKUP($A125,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業法違反</v>
       </c>
-      <c r="H125" t="str">
+      <c r="I125" t="str">
         <f>IF($A125="","",VLOOKUP($A125,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業法違反</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -4630,28 +4771,30 @@
         <f>IF($A126="","",VLOOKUP($A126,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D126" s="5"/>
+      <c r="D126"/>
       <c r="E126" s="5"/>
-      <c r="F126" t="str">
+      <c r="F126" s="5"/>
+      <c r="G126" t="str">
         <f>IF($A126="","",VLOOKUP($A126,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者の名義貸しは禁止</v>
       </c>
-      <c r="H126" t="str">
+      <c r="I126" t="str">
         <f>IF($A126="","",VLOOKUP($A126,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者の名義貸しは禁止</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="37.5">
-      <c r="A127" t="str">
+    <row r="127" spans="1:9" s="9" customFormat="1" ht="37.5">
+      <c r="A127" s="9" t="str">
         <f>"Q"&amp;ROW()-1</f>
         <v>Q126</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" s="10" t="s">
         <v>424</v>
       </c>
+      <c r="D127" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/data/SBKnowledgeData.xlsx
+++ b/data/SBKnowledgeData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\SBFlash\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70B71DC-E270-4E48-948D-EBAD8474EBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D5D220-B310-4EB9-A044-63575862200A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30135" yWindow="3990" windowWidth="23550" windowHeight="9015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="825" yWindow="3135" windowWidth="25740" windowHeight="9435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宅建業法" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="431">
   <si>
     <t>№</t>
   </si>
@@ -1339,6 +1339,95 @@
     <t>語呂合わせ</t>
     <rPh sb="0" eb="3">
       <t>ゴロア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>預けるお金に種類</t>
+    <rPh sb="0" eb="1">
+      <t>アズ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>営業保証金、弁済業務保証金</t>
+    <rPh sb="0" eb="2">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホショウキン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ベンサイギョウム</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ホショウキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>営業保証金の仕組み</t>
+    <rPh sb="0" eb="2">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホショウキン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>供託、還付、取戻</t>
+    <rPh sb="0" eb="2">
+      <t>キョウタク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンプ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トリモドシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日（二重供託）本（保証会加入）刀（10年経過）いらない（公告は不要）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ニジュウキョウタク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ホショウカイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カニュウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カタナ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>フヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1737,15 +1826,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
     <col min="2" max="2" width="40.625" customWidth="1"/>
     <col min="3" max="3" width="44.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="39.875" style="3" customWidth="1"/>
-    <col min="5" max="6" width="26.125" customWidth="1"/>
-    <col min="7" max="7" width="50.5" customWidth="1"/>
+    <col min="4" max="5" width="26.125" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="39.875" style="3" customWidth="1"/>
     <col min="8" max="8" width="22.25" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
     <col min="10" max="10" width="19.375" customWidth="1"/>
@@ -1762,16 +1851,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>425</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -1795,13 +1884,13 @@
         <f>IF($A2="","",VLOOKUP($A2,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" t="str">
+      <c r="F2" t="str">
         <f>IF($A2="","",VLOOKUP($A2,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は道路・公園など公共施設を除き宅地となる</v>
       </c>
+      <c r="G2"/>
       <c r="I2" t="str">
         <f>IF($A2="","",VLOOKUP($A2,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は道路・公園など公共施設を除き宅地となる</v>
@@ -1819,13 +1908,13 @@
         <f>IF($A3="","",VLOOKUP($A3,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" t="str">
+      <c r="F3" t="str">
         <f>IF($A3="","",VLOOKUP($A3,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は現況に関係なく宅地となる</v>
       </c>
+      <c r="G3"/>
       <c r="I3" t="str">
         <f>IF($A3="","",VLOOKUP($A3,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域内の土地は現況に関係なく宅地となる</v>
@@ -1843,13 +1932,13 @@
         <f>IF($A4="","",VLOOKUP($A4,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D4"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" t="str">
+      <c r="F4" t="str">
         <f>IF($A4="","",VLOOKUP($A4,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域外でも建物敷地として使用される土地は宅地</v>
       </c>
+      <c r="G4"/>
       <c r="I4" t="str">
         <f>IF($A4="","",VLOOKUP($A4,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>用途地域外でも建物敷地として使用される土地は宅地</v>
@@ -1867,13 +1956,13 @@
         <f>IF($A5="","",VLOOKUP($A5,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D5"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" t="str">
+      <c r="F5" t="str">
         <f>IF($A5="","",VLOOKUP($A5,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>道路・河川・公園など公共施設の用地は宅地ではない</v>
       </c>
+      <c r="G5"/>
       <c r="I5" t="str">
         <f>IF($A5="","",VLOOKUP($A5,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>道路・河川・公園など公共施設の用地は宅地ではない</v>
@@ -1891,13 +1980,13 @@
         <f>IF($A6="","",VLOOKUP($A6,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D6"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" t="str">
+      <c r="F6" t="str">
         <f>IF($A6="","",VLOOKUP($A6,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>建物敷地以外でも宅地に該当する場合がある</v>
       </c>
+      <c r="G6"/>
       <c r="I6" t="str">
         <f>IF($A6="","",VLOOKUP($A6,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>建物敷地以外でも宅地に該当する場合がある</v>
@@ -1915,13 +2004,13 @@
         <f>IF($A7="","",VLOOKUP($A7,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D7"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" t="str">
+      <c r="F7" t="str">
         <f>IF($A7="","",VLOOKUP($A7,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業は反復継続が必要</v>
       </c>
+      <c r="G7"/>
       <c r="I7" t="str">
         <f>IF($A7="","",VLOOKUP($A7,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業は反復継続が必要</v>
@@ -1939,13 +2028,13 @@
         <f>IF($A8="","",VLOOKUP($A8,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D8"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" t="str">
+      <c r="F8" t="str">
         <f>IF($A8="","",VLOOKUP($A8,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>反復継続して売買する場合は宅建業</v>
       </c>
+      <c r="G8"/>
       <c r="I8" t="str">
         <f>IF($A8="","",VLOOKUP($A8,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>反復継続して売買する場合は宅建業</v>
@@ -1963,13 +2052,13 @@
         <f>IF($A9="","",VLOOKUP($A9,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D9"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" t="str">
+      <c r="F9" t="str">
         <f>IF($A9="","",VLOOKUP($A9,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>賃貸の代理・媒介は宅建業</v>
       </c>
+      <c r="G9"/>
       <c r="I9" t="str">
         <f>IF($A9="","",VLOOKUP($A9,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>賃貸の代理・媒介は宅建業</v>
@@ -1987,13 +2076,13 @@
         <f>IF($A10="","",VLOOKUP($A10,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D10"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" t="str">
+      <c r="F10" t="str">
         <f>IF($A10="","",VLOOKUP($A10,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>貸借は宅建業に含まれない</v>
       </c>
+      <c r="G10"/>
       <c r="I10" t="str">
         <f>IF($A10="","",VLOOKUP($A10,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>貸借は宅建業に含まれない</v>
@@ -2011,13 +2100,13 @@
         <f>IF($A11="","",VLOOKUP($A11,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D11"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" t="str">
+      <c r="F11" t="str">
         <f>IF($A11="","",VLOOKUP($A11,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売買の媒介は宅建業</v>
       </c>
+      <c r="G11"/>
       <c r="I11" t="str">
         <f>IF($A11="","",VLOOKUP($A11,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売買の媒介は宅建業</v>
@@ -2035,13 +2124,13 @@
         <f>IF($A12="","",VLOOKUP($A12,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D12"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" t="str">
+      <c r="F12" t="str">
         <f>IF($A12="","",VLOOKUP($A12,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業免許は5年ごと更新</v>
       </c>
+      <c r="G12"/>
       <c r="I12" t="str">
         <f>IF($A12="","",VLOOKUP($A12,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業免許は5年ごと更新</v>
@@ -2059,13 +2148,13 @@
         <f>IF($A13="","",VLOOKUP($A13,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D13"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" t="str">
+      <c r="F13" t="str">
         <f>IF($A13="","",VLOOKUP($A13,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>満了前に申請必要</v>
       </c>
+      <c r="G13"/>
       <c r="I13" t="str">
         <f>IF($A13="","",VLOOKUP($A13,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>満了前に申請必要</v>
@@ -2083,13 +2172,13 @@
         <f>IF($A14="","",VLOOKUP($A14,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D14"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" t="str">
+      <c r="F14" t="str">
         <f>IF($A14="","",VLOOKUP($A14,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>複数都道府県は大臣免許</v>
       </c>
+      <c r="G14"/>
       <c r="I14" t="str">
         <f>IF($A14="","",VLOOKUP($A14,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>複数都道府県は大臣免許</v>
@@ -2107,13 +2196,13 @@
         <f>IF($A15="","",VLOOKUP($A15,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D15"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" t="str">
+      <c r="F15" t="str">
         <f>IF($A15="","",VLOOKUP($A15,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>単一都道府県は知事免許</v>
       </c>
+      <c r="G15"/>
       <c r="I15" t="str">
         <f>IF($A15="","",VLOOKUP($A15,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>単一都道府県は知事免許</v>
@@ -2131,13 +2220,13 @@
         <f>IF($A16="","",VLOOKUP($A16,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D16"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" t="str">
+      <c r="F16" t="str">
         <f>IF($A16="","",VLOOKUP($A16,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>免許が必要</v>
       </c>
+      <c r="G16"/>
       <c r="I16" t="str">
         <f>IF($A16="","",VLOOKUP($A16,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>免許が必要</v>
@@ -2155,13 +2244,13 @@
         <f>IF($A17="","",VLOOKUP($A17,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D17"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" t="str">
+      <c r="F17" t="str">
         <f>IF($A17="","",VLOOKUP($A17,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士が説明</v>
       </c>
+      <c r="G17"/>
       <c r="I17" t="str">
         <f>IF($A17="","",VLOOKUP($A17,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士が説明</v>
@@ -2179,13 +2268,13 @@
         <f>IF($A18="","",VLOOKUP($A18,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D18"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" t="str">
+      <c r="F18" t="str">
         <f>IF($A18="","",VLOOKUP($A18,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明が必要</v>
       </c>
+      <c r="G18"/>
       <c r="I18" t="str">
         <f>IF($A18="","",VLOOKUP($A18,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明が必要</v>
@@ -2203,13 +2292,13 @@
         <f>IF($A19="","",VLOOKUP($A19,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D19"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" t="str">
+      <c r="F19" t="str">
         <f>IF($A19="","",VLOOKUP($A19,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>5年</v>
       </c>
+      <c r="G19"/>
       <c r="I19" t="str">
         <f>IF($A19="","",VLOOKUP($A19,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>5年</v>
@@ -2227,13 +2316,13 @@
         <f>IF($A20="","",VLOOKUP($A20,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D20"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" t="str">
+      <c r="F20" t="str">
         <f>IF($A20="","",VLOOKUP($A20,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>法定講習必要</v>
       </c>
+      <c r="G20"/>
       <c r="I20" t="str">
         <f>IF($A20="","",VLOOKUP($A20,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>法定講習必要</v>
@@ -2251,13 +2340,13 @@
         <f>IF($A21="","",VLOOKUP($A21,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D21"/>
+      <c r="D21" s="5"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" t="str">
+      <c r="F21" t="str">
         <f>IF($A21="","",VLOOKUP($A21,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士のみ</v>
       </c>
+      <c r="G21"/>
       <c r="I21" t="str">
         <f>IF($A21="","",VLOOKUP($A21,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士のみ</v>
@@ -2275,13 +2364,13 @@
         <f>IF($A22="","",VLOOKUP($A22,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D22"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" t="str">
+      <c r="F22" t="str">
         <f>IF($A22="","",VLOOKUP($A22,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>主事務所1000万</v>
       </c>
+      <c r="G22"/>
       <c r="I22" t="str">
         <f>IF($A22="","",VLOOKUP($A22,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>主事務所1000万</v>
@@ -2299,13 +2388,13 @@
         <f>IF($A23="","",VLOOKUP($A23,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D23"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" t="str">
+      <c r="F23" t="str">
         <f>IF($A23="","",VLOOKUP($A23,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>500万</v>
       </c>
+      <c r="G23"/>
       <c r="I23" t="str">
         <f>IF($A23="","",VLOOKUP($A23,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>500万</v>
@@ -2323,13 +2412,13 @@
         <f>IF($A24="","",VLOOKUP($A24,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D24"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" t="str">
+      <c r="F24" t="str">
         <f>IF($A24="","",VLOOKUP($A24,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>届出必要</v>
       </c>
+      <c r="G24"/>
       <c r="I24" t="str">
         <f>IF($A24="","",VLOOKUP($A24,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>届出必要</v>
@@ -2347,13 +2436,13 @@
         <f>IF($A25="","",VLOOKUP($A25,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D25"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" t="str">
+      <c r="F25" t="str">
         <f>IF($A25="","",VLOOKUP($A25,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>分担金制度</v>
       </c>
+      <c r="G25"/>
       <c r="I25" t="str">
         <f>IF($A25="","",VLOOKUP($A25,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>分担金制度</v>
@@ -2371,13 +2460,13 @@
         <f>IF($A26="","",VLOOKUP($A26,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D26"/>
+      <c r="D26" s="5"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" t="str">
+      <c r="F26" t="str">
         <f>IF($A26="","",VLOOKUP($A26,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>1団体のみ</v>
       </c>
+      <c r="G26"/>
       <c r="I26" t="str">
         <f>IF($A26="","",VLOOKUP($A26,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>1団体のみ</v>
@@ -2395,13 +2484,13 @@
         <f>IF($A27="","",VLOOKUP($A27,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D27"/>
+      <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" t="str">
+      <c r="F27" t="str">
         <f>IF($A27="","",VLOOKUP($A27,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約前</v>
       </c>
+      <c r="G27"/>
       <c r="I27" t="str">
         <f>IF($A27="","",VLOOKUP($A27,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約前</v>
@@ -2419,13 +2508,13 @@
         <f>IF($A28="","",VLOOKUP($A28,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D28"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" t="str">
+      <c r="F28" t="str">
         <f>IF($A28="","",VLOOKUP($A28,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士説明</v>
       </c>
+      <c r="G28"/>
       <c r="I28" t="str">
         <f>IF($A28="","",VLOOKUP($A28,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建士説明</v>
@@ -2443,13 +2532,13 @@
         <f>IF($A29="","",VLOOKUP($A29,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D29"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" t="str">
+      <c r="F29" t="str">
         <f>IF($A29="","",VLOOKUP($A29,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面必要</v>
       </c>
+      <c r="G29"/>
       <c r="I29" t="str">
         <f>IF($A29="","",VLOOKUP($A29,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面必要</v>
@@ -2467,13 +2556,13 @@
         <f>IF($A30="","",VLOOKUP($A30,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D30"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" t="str">
+      <c r="F30" t="str">
         <f>IF($A30="","",VLOOKUP($A30,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
+      <c r="G30"/>
       <c r="I30" t="str">
         <f>IF($A30="","",VLOOKUP($A30,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
@@ -2491,13 +2580,13 @@
         <f>IF($A31="","",VLOOKUP($A31,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D31"/>
+      <c r="D31" s="5"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" t="str">
+      <c r="F31" t="str">
         <f>IF($A31="","",VLOOKUP($A31,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定条件で可能</v>
       </c>
+      <c r="G31"/>
       <c r="I31" t="str">
         <f>IF($A31="","",VLOOKUP($A31,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定条件で可能</v>
@@ -2515,13 +2604,13 @@
         <f>IF($A32="","",VLOOKUP($A32,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D32"/>
+      <c r="D32" s="5"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" t="str">
+      <c r="F32" t="str">
         <f>IF($A32="","",VLOOKUP($A32,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約成立後</v>
       </c>
+      <c r="G32"/>
       <c r="I32" t="str">
         <f>IF($A32="","",VLOOKUP($A32,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約成立後</v>
@@ -2539,13 +2628,13 @@
         <f>IF($A33="","",VLOOKUP($A33,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D33"/>
+      <c r="D33" s="5"/>
       <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" t="str">
+      <c r="F33" t="str">
         <f>IF($A33="","",VLOOKUP($A33,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明不要</v>
       </c>
+      <c r="G33"/>
       <c r="I33" t="str">
         <f>IF($A33="","",VLOOKUP($A33,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>説明不要</v>
@@ -2563,13 +2652,13 @@
         <f>IF($A34="","",VLOOKUP($A34,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D34"/>
+      <c r="D34" s="5"/>
       <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" t="str">
+      <c r="F34" t="str">
         <f>IF($A34="","",VLOOKUP($A34,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
+      <c r="G34"/>
       <c r="I34" t="str">
         <f>IF($A34="","",VLOOKUP($A34,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
@@ -2587,13 +2676,13 @@
         <f>IF($A35="","",VLOOKUP($A35,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D35"/>
+      <c r="D35" s="5"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" t="str">
+      <c r="F35" t="str">
         <f>IF($A35="","",VLOOKUP($A35,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約後</v>
       </c>
+      <c r="G35"/>
       <c r="I35" t="str">
         <f>IF($A35="","",VLOOKUP($A35,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約後</v>
@@ -2611,13 +2700,13 @@
         <f>IF($A36="","",VLOOKUP($A36,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D36"/>
+      <c r="D36" s="5"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" t="str">
+      <c r="F36" t="str">
         <f>IF($A36="","",VLOOKUP($A36,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
+      <c r="G36"/>
       <c r="I36" t="str">
         <f>IF($A36="","",VLOOKUP($A36,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
@@ -2635,13 +2724,13 @@
         <f>IF($A37="","",VLOOKUP($A37,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D37"/>
+      <c r="D37" s="5"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" t="str">
+      <c r="F37" t="str">
         <f>IF($A37="","",VLOOKUP($A37,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
       </c>
+      <c r="G37"/>
       <c r="I37" t="str">
         <f>IF($A37="","",VLOOKUP($A37,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
@@ -2659,13 +2748,13 @@
         <f>IF($A38="","",VLOOKUP($A38,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D38"/>
+      <c r="D38" s="5"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" t="str">
+      <c r="F38" t="str">
         <f>IF($A38="","",VLOOKUP($A38,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
+      <c r="G38"/>
       <c r="I38" t="str">
         <f>IF($A38="","",VLOOKUP($A38,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
@@ -2683,13 +2772,13 @@
         <f>IF($A39="","",VLOOKUP($A39,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D39"/>
+      <c r="D39" s="5"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" t="str">
+      <c r="F39" t="str">
         <f>IF($A39="","",VLOOKUP($A39,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
+      <c r="G39"/>
       <c r="I39" t="str">
         <f>IF($A39="","",VLOOKUP($A39,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
@@ -2707,13 +2796,13 @@
         <f>IF($A40="","",VLOOKUP($A40,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D40"/>
+      <c r="D40" s="5"/>
       <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" t="str">
+      <c r="F40" t="str">
         <f>IF($A40="","",VLOOKUP($A40,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
       </c>
+      <c r="G40"/>
       <c r="I40" t="str">
         <f>IF($A40="","",VLOOKUP($A40,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>禁止</v>
@@ -2731,13 +2820,13 @@
         <f>IF($A41="","",VLOOKUP($A41,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D41"/>
+      <c r="D41" s="5"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" t="str">
+      <c r="F41" t="str">
         <f>IF($A41="","",VLOOKUP($A41,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
+      <c r="G41"/>
       <c r="I41" t="str">
         <f>IF($A41="","",VLOOKUP($A41,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
@@ -2755,13 +2844,13 @@
         <f>IF($A42="","",VLOOKUP($A42,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D42"/>
+      <c r="D42" s="5"/>
       <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" t="str">
+      <c r="F42" t="str">
         <f>IF($A42="","",VLOOKUP($A42,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
       </c>
+      <c r="G42"/>
       <c r="I42" t="str">
         <f>IF($A42="","",VLOOKUP($A42,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
@@ -2779,13 +2868,13 @@
         <f>IF($A43="","",VLOOKUP($A43,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D43"/>
+      <c r="D43" s="5"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" t="str">
+      <c r="F43" t="str">
         <f>IF($A43="","",VLOOKUP($A43,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
+      <c r="G43"/>
       <c r="I43" t="str">
         <f>IF($A43="","",VLOOKUP($A43,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
@@ -2803,13 +2892,13 @@
         <f>IF($A44="","",VLOOKUP($A44,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D44"/>
+      <c r="D44" s="5"/>
       <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" t="str">
+      <c r="F44" t="str">
         <f>IF($A44="","",VLOOKUP($A44,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
+      <c r="G44"/>
       <c r="I44" t="str">
         <f>IF($A44="","",VLOOKUP($A44,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
@@ -2827,13 +2916,13 @@
         <f>IF($A45="","",VLOOKUP($A45,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D45"/>
+      <c r="D45" s="5"/>
       <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" t="str">
+      <c r="F45" t="str">
         <f>IF($A45="","",VLOOKUP($A45,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G45"/>
       <c r="I45" t="str">
         <f>IF($A45="","",VLOOKUP($A45,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -2851,13 +2940,13 @@
         <f>IF($A46="","",VLOOKUP($A46,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D46"/>
+      <c r="D46" s="5"/>
       <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" t="str">
+      <c r="F46" t="str">
         <f>IF($A46="","",VLOOKUP($A46,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G46"/>
       <c r="I46" t="str">
         <f>IF($A46="","",VLOOKUP($A46,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -2875,13 +2964,13 @@
         <f>IF($A47="","",VLOOKUP($A47,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D47"/>
+      <c r="D47" s="5"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" t="str">
+      <c r="F47" t="str">
         <f>IF($A47="","",VLOOKUP($A47,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>20％以内</v>
       </c>
+      <c r="G47"/>
       <c r="I47" t="str">
         <f>IF($A47="","",VLOOKUP($A47,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>20％以内</v>
@@ -2899,13 +2988,13 @@
         <f>IF($A48="","",VLOOKUP($A48,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D48"/>
+      <c r="D48" s="5"/>
       <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" t="str">
+      <c r="F48" t="str">
         <f>IF($A48="","",VLOOKUP($A48,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G48"/>
       <c r="I48" t="str">
         <f>IF($A48="","",VLOOKUP($A48,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -2923,13 +3012,13 @@
         <f>IF($A49="","",VLOOKUP($A49,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D49"/>
+      <c r="D49" s="5"/>
       <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" t="str">
+      <c r="F49" t="str">
         <f>IF($A49="","",VLOOKUP($A49,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>以内</v>
       </c>
+      <c r="G49"/>
       <c r="I49" t="str">
         <f>IF($A49="","",VLOOKUP($A49,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>以内</v>
@@ -2947,13 +3036,13 @@
         <f>IF($A50="","",VLOOKUP($A50,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D50"/>
+      <c r="D50" s="5"/>
       <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" t="str">
+      <c r="F50" t="str">
         <f>IF($A50="","",VLOOKUP($A50,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
       </c>
+      <c r="G50"/>
       <c r="I50" t="str">
         <f>IF($A50="","",VLOOKUP($A50,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>可能</v>
@@ -2971,13 +3060,13 @@
         <f>IF($A51="","",VLOOKUP($A51,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D51"/>
+      <c r="D51" s="5"/>
       <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" t="str">
+      <c r="F51" t="str">
         <f>IF($A51="","",VLOOKUP($A51,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主のみ</v>
       </c>
+      <c r="G51"/>
       <c r="I51" t="str">
         <f>IF($A51="","",VLOOKUP($A51,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主のみ</v>
@@ -2995,13 +3084,13 @@
         <f>IF($A52="","",VLOOKUP($A52,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D52"/>
+      <c r="D52" s="5"/>
       <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" t="str">
+      <c r="F52" t="str">
         <f>IF($A52="","",VLOOKUP($A52,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
+      <c r="G52"/>
       <c r="I52" t="str">
         <f>IF($A52="","",VLOOKUP($A52,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
@@ -3019,13 +3108,13 @@
         <f>IF($A53="","",VLOOKUP($A53,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D53"/>
+      <c r="D53" s="5"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" t="str">
+      <c r="F53" t="str">
         <f>IF($A53="","",VLOOKUP($A53,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
+      <c r="G53"/>
       <c r="I53" t="str">
         <f>IF($A53="","",VLOOKUP($A53,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
@@ -3043,13 +3132,13 @@
         <f>IF($A54="","",VLOOKUP($A54,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D54"/>
+      <c r="D54" s="5"/>
       <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" t="str">
+      <c r="F54" t="str">
         <f>IF($A54="","",VLOOKUP($A54,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>成立時</v>
       </c>
+      <c r="G54"/>
       <c r="I54" t="str">
         <f>IF($A54="","",VLOOKUP($A54,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>成立時</v>
@@ -3067,13 +3156,13 @@
         <f>IF($A55="","",VLOOKUP($A55,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D55"/>
+      <c r="D55" s="5"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" t="str">
+      <c r="F55" t="str">
         <f>IF($A55="","",VLOOKUP($A55,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>告示</v>
       </c>
+      <c r="G55"/>
       <c r="I55" t="str">
         <f>IF($A55="","",VLOOKUP($A55,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>告示</v>
@@ -3091,13 +3180,13 @@
         <f>IF($A56="","",VLOOKUP($A56,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D56"/>
+      <c r="D56" s="5"/>
       <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" t="str">
+      <c r="F56" t="str">
         <f>IF($A56="","",VLOOKUP($A56,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>上限あり</v>
       </c>
+      <c r="G56"/>
       <c r="I56" t="str">
         <f>IF($A56="","",VLOOKUP($A56,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>上限あり</v>
@@ -3115,13 +3204,13 @@
         <f>IF($A57="","",VLOOKUP($A57,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D57"/>
+      <c r="D57" s="5"/>
       <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" t="str">
+      <c r="F57" t="str">
         <f>IF($A57="","",VLOOKUP($A57,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G57"/>
       <c r="I57" t="str">
         <f>IF($A57="","",VLOOKUP($A57,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3139,13 +3228,13 @@
         <f>IF($A58="","",VLOOKUP($A58,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D58"/>
+      <c r="D58" s="5"/>
       <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" t="str">
+      <c r="F58" t="str">
         <f>IF($A58="","",VLOOKUP($A58,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G58"/>
       <c r="I58" t="str">
         <f>IF($A58="","",VLOOKUP($A58,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3163,13 +3252,13 @@
         <f>IF($A59="","",VLOOKUP($A59,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D59"/>
+      <c r="D59" s="5"/>
       <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" t="str">
+      <c r="F59" t="str">
         <f>IF($A59="","",VLOOKUP($A59,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G59"/>
       <c r="I59" t="str">
         <f>IF($A59="","",VLOOKUP($A59,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3187,13 +3276,13 @@
         <f>IF($A60="","",VLOOKUP($A60,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D60"/>
+      <c r="D60" s="5"/>
       <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" t="str">
+      <c r="F60" t="str">
         <f>IF($A60="","",VLOOKUP($A60,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>大臣も可</v>
       </c>
+      <c r="G60"/>
       <c r="I60" t="str">
         <f>IF($A60="","",VLOOKUP($A60,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>大臣も可</v>
@@ -3211,13 +3300,13 @@
         <f>IF($A61="","",VLOOKUP($A61,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D61"/>
+      <c r="D61" s="5"/>
       <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" t="str">
+      <c r="F61" t="str">
         <f>IF($A61="","",VLOOKUP($A61,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G61"/>
       <c r="I61" t="str">
         <f>IF($A61="","",VLOOKUP($A61,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3235,13 +3324,13 @@
         <f>IF($A62="","",VLOOKUP($A62,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D62"/>
+      <c r="D62" s="5"/>
       <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" t="str">
+      <c r="F62" t="str">
         <f>IF($A62="","",VLOOKUP($A62,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G62"/>
       <c r="I62" t="str">
         <f>IF($A62="","",VLOOKUP($A62,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3259,13 +3348,13 @@
         <f>IF($A63="","",VLOOKUP($A63,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D63"/>
+      <c r="D63" s="5"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" t="str">
+      <c r="F63" t="str">
         <f>IF($A63="","",VLOOKUP($A63,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G63"/>
       <c r="I63" t="str">
         <f>IF($A63="","",VLOOKUP($A63,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3283,13 +3372,13 @@
         <f>IF($A64="","",VLOOKUP($A64,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D64"/>
+      <c r="D64" s="5"/>
       <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" t="str">
+      <c r="F64" t="str">
         <f>IF($A64="","",VLOOKUP($A64,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G64"/>
       <c r="I64" t="str">
         <f>IF($A64="","",VLOOKUP($A64,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3307,13 +3396,13 @@
         <f>IF($A65="","",VLOOKUP($A65,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D65"/>
+      <c r="D65" s="5"/>
       <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" t="str">
+      <c r="F65" t="str">
         <f>IF($A65="","",VLOOKUP($A65,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G65"/>
       <c r="I65" t="str">
         <f>IF($A65="","",VLOOKUP($A65,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3331,13 +3420,13 @@
         <f>IF($A66="","",VLOOKUP($A66,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D66"/>
+      <c r="D66" s="5"/>
       <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" t="str">
+      <c r="F66" t="str">
         <f>IF($A66="","",VLOOKUP($A66,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G66"/>
       <c r="I66" t="str">
         <f>IF($A66="","",VLOOKUP($A66,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3355,13 +3444,13 @@
         <f>IF($A67="","",VLOOKUP($A67,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D67"/>
+      <c r="D67" s="5"/>
       <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" t="str">
+      <c r="F67" t="str">
         <f>IF($A67="","",VLOOKUP($A67,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>提示</v>
       </c>
+      <c r="G67"/>
       <c r="I67" t="str">
         <f>IF($A67="","",VLOOKUP($A67,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>提示</v>
@@ -3379,13 +3468,13 @@
         <f>IF($A68="","",VLOOKUP($A68,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D68"/>
+      <c r="D68" s="5"/>
       <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" t="str">
+      <c r="F68" t="str">
         <f>IF($A68="","",VLOOKUP($A68,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>携帯</v>
       </c>
+      <c r="G68"/>
       <c r="I68" t="str">
         <f>IF($A68="","",VLOOKUP($A68,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>携帯</v>
@@ -3403,13 +3492,13 @@
         <f>IF($A69="","",VLOOKUP($A69,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D69"/>
+      <c r="D69" s="5"/>
       <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" t="str">
+      <c r="F69" t="str">
         <f>IF($A69="","",VLOOKUP($A69,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G69"/>
       <c r="I69" t="str">
         <f>IF($A69="","",VLOOKUP($A69,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3427,13 +3516,13 @@
         <f>IF($A70="","",VLOOKUP($A70,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D70"/>
+      <c r="D70" s="5"/>
       <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" t="str">
+      <c r="F70" t="str">
         <f>IF($A70="","",VLOOKUP($A70,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
+      <c r="G70"/>
       <c r="I70" t="str">
         <f>IF($A70="","",VLOOKUP($A70,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
@@ -3451,13 +3540,13 @@
         <f>IF($A71="","",VLOOKUP($A71,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D71"/>
+      <c r="D71" s="5"/>
       <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" t="str">
+      <c r="F71" t="str">
         <f>IF($A71="","",VLOOKUP($A71,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G71"/>
       <c r="I71" t="str">
         <f>IF($A71="","",VLOOKUP($A71,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3475,13 +3564,13 @@
         <f>IF($A72="","",VLOOKUP($A72,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D72"/>
+      <c r="D72" s="5"/>
       <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" t="str">
+      <c r="F72" t="str">
         <f>IF($A72="","",VLOOKUP($A72,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
+      <c r="G72"/>
       <c r="I72" t="str">
         <f>IF($A72="","",VLOOKUP($A72,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
@@ -3499,13 +3588,13 @@
         <f>IF($A73="","",VLOOKUP($A73,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D73"/>
+      <c r="D73" s="5"/>
       <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" t="str">
+      <c r="F73" t="str">
         <f>IF($A73="","",VLOOKUP($A73,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
       </c>
+      <c r="G73"/>
       <c r="I73" t="str">
         <f>IF($A73="","",VLOOKUP($A73,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>ある</v>
@@ -3523,13 +3612,13 @@
         <f>IF($A74="","",VLOOKUP($A74,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D74"/>
+      <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" t="str">
+      <c r="F74" t="str">
         <f>IF($A74="","",VLOOKUP($A74,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G74"/>
       <c r="I74" t="str">
         <f>IF($A74="","",VLOOKUP($A74,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3547,13 +3636,13 @@
         <f>IF($A75="","",VLOOKUP($A75,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D75"/>
+      <c r="D75" s="5"/>
       <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" t="str">
+      <c r="F75" t="str">
         <f>IF($A75="","",VLOOKUP($A75,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
       </c>
+      <c r="G75"/>
       <c r="I75" t="str">
         <f>IF($A75="","",VLOOKUP($A75,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>不可</v>
@@ -3571,13 +3660,13 @@
         <f>IF($A76="","",VLOOKUP($A76,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D76"/>
+      <c r="D76" s="5"/>
       <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" t="str">
+      <c r="F76" t="str">
         <f>IF($A76="","",VLOOKUP($A76,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>別</v>
       </c>
+      <c r="G76"/>
       <c r="I76" t="str">
         <f>IF($A76="","",VLOOKUP($A76,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>別</v>
@@ -3595,13 +3684,13 @@
         <f>IF($A77="","",VLOOKUP($A77,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D77"/>
+      <c r="D77" s="5"/>
       <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" t="str">
+      <c r="F77" t="str">
         <f>IF($A77="","",VLOOKUP($A77,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G77"/>
       <c r="I77" t="str">
         <f>IF($A77="","",VLOOKUP($A77,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3619,13 +3708,13 @@
         <f>IF($A78="","",VLOOKUP($A78,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D78"/>
+      <c r="D78" s="5"/>
       <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" t="str">
+      <c r="F78" t="str">
         <f>IF($A78="","",VLOOKUP($A78,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G78"/>
       <c r="I78" t="str">
         <f>IF($A78="","",VLOOKUP($A78,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3643,13 +3732,13 @@
         <f>IF($A79="","",VLOOKUP($A79,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D79"/>
+      <c r="D79" s="5"/>
       <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" t="str">
+      <c r="F79" t="str">
         <f>IF($A79="","",VLOOKUP($A79,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G79"/>
       <c r="I79" t="str">
         <f>IF($A79="","",VLOOKUP($A79,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3667,13 +3756,13 @@
         <f>IF($A80="","",VLOOKUP($A80,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D80"/>
+      <c r="D80" s="5"/>
       <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" t="str">
+      <c r="F80" t="str">
         <f>IF($A80="","",VLOOKUP($A80,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
       </c>
+      <c r="G80"/>
       <c r="I80" t="str">
         <f>IF($A80="","",VLOOKUP($A80,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>あり</v>
@@ -3691,13 +3780,13 @@
         <f>IF($A81="","",VLOOKUP($A81,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D81"/>
+      <c r="D81" s="5"/>
       <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" t="str">
+      <c r="F81" t="str">
         <f>IF($A81="","",VLOOKUP($A81,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
       </c>
+      <c r="G81"/>
       <c r="I81" t="str">
         <f>IF($A81="","",VLOOKUP($A81,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>必要</v>
@@ -3715,13 +3804,13 @@
         <f>IF($A82="","",VLOOKUP($A82,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D82"/>
+      <c r="D82" s="5"/>
       <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" t="str">
+      <c r="F82" t="str">
         <f>IF($A82="","",VLOOKUP($A82,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者は免許を受ける前に広告を出してはならない</v>
       </c>
+      <c r="G82"/>
       <c r="I82" t="str">
         <f>IF($A82="","",VLOOKUP($A82,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者は免許を受ける前に広告を出してはならない</v>
@@ -3739,13 +3828,13 @@
         <f>IF($A83="","",VLOOKUP($A83,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D83"/>
+      <c r="D83" s="5"/>
       <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" t="str">
+      <c r="F83" t="str">
         <f>IF($A83="","",VLOOKUP($A83,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売主・代理・媒介など取引態様の明示が必要</v>
       </c>
+      <c r="G83"/>
       <c r="I83" t="str">
         <f>IF($A83="","",VLOOKUP($A83,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>売主・代理・媒介など取引態様の明示が必要</v>
@@ -3763,13 +3852,13 @@
         <f>IF($A84="","",VLOOKUP($A84,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D84"/>
+      <c r="D84" s="5"/>
       <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" t="str">
+      <c r="F84" t="str">
         <f>IF($A84="","",VLOOKUP($A84,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>著しく事実に相違する広告は禁止されている</v>
       </c>
+      <c r="G84"/>
       <c r="I84" t="str">
         <f>IF($A84="","",VLOOKUP($A84,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>著しく事実に相違する広告は禁止されている</v>
@@ -3787,13 +3876,13 @@
         <f>IF($A85="","",VLOOKUP($A85,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D85"/>
+      <c r="D85" s="5"/>
       <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" t="str">
+      <c r="F85" t="str">
         <f>IF($A85="","",VLOOKUP($A85,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>造成工事完了前の広告には制限がある</v>
       </c>
+      <c r="G85"/>
       <c r="I85" t="str">
         <f>IF($A85="","",VLOOKUP($A85,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>造成工事完了前の広告には制限がある</v>
@@ -3811,13 +3900,13 @@
         <f>IF($A86="","",VLOOKUP($A86,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D86"/>
+      <c r="D86" s="5"/>
       <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" t="str">
+      <c r="F86" t="str">
         <f>IF($A86="","",VLOOKUP($A86,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>許可番号などの表示が必要</v>
       </c>
+      <c r="G86"/>
       <c r="I86" t="str">
         <f>IF($A86="","",VLOOKUP($A86,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>許可番号などの表示が必要</v>
@@ -3835,13 +3924,13 @@
         <f>IF($A87="","",VLOOKUP($A87,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D87"/>
+      <c r="D87" s="5"/>
       <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" t="str">
+      <c r="F87" t="str">
         <f>IF($A87="","",VLOOKUP($A87,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介、専任媒介、専属専任媒介</v>
       </c>
+      <c r="G87"/>
       <c r="I87" t="str">
         <f>IF($A87="","",VLOOKUP($A87,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介、専任媒介、専属専任媒介</v>
@@ -3859,13 +3948,13 @@
         <f>IF($A88="","",VLOOKUP($A88,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D88"/>
+      <c r="D88" s="5"/>
       <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" t="str">
+      <c r="F88" t="str">
         <f>IF($A88="","",VLOOKUP($A88,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専属専任媒介では自己発見取引は禁止</v>
       </c>
+      <c r="G88"/>
       <c r="I88" t="str">
         <f>IF($A88="","",VLOOKUP($A88,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専属専任媒介では自己発見取引は禁止</v>
@@ -3883,13 +3972,13 @@
         <f>IF($A89="","",VLOOKUP($A89,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D89"/>
+      <c r="D89" s="5"/>
       <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" t="str">
+      <c r="F89" t="str">
         <f>IF($A89="","",VLOOKUP($A89,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介では自己発見取引は可能</v>
       </c>
+      <c r="G89"/>
       <c r="I89" t="str">
         <f>IF($A89="","",VLOOKUP($A89,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介では自己発見取引は可能</v>
@@ -3907,13 +3996,13 @@
         <f>IF($A90="","",VLOOKUP($A90,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D90"/>
+      <c r="D90" s="5"/>
       <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" t="str">
+      <c r="F90" t="str">
         <f>IF($A90="","",VLOOKUP($A90,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約は書面交付が必要</v>
       </c>
+      <c r="G90"/>
       <c r="I90" t="str">
         <f>IF($A90="","",VLOOKUP($A90,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約は書面交付が必要</v>
@@ -3931,13 +4020,13 @@
         <f>IF($A91="","",VLOOKUP($A91,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D91"/>
+      <c r="D91" s="5"/>
       <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" t="str">
+      <c r="F91" t="str">
         <f>IF($A91="","",VLOOKUP($A91,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約の期間は3か月以内</v>
       </c>
+      <c r="G91"/>
       <c r="I91" t="str">
         <f>IF($A91="","",VLOOKUP($A91,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>媒介契約の期間は3か月以内</v>
@@ -3955,13 +4044,13 @@
         <f>IF($A92="","",VLOOKUP($A92,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D92"/>
+      <c r="D92" s="5"/>
       <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" t="str">
+      <c r="F92" t="str">
         <f>IF($A92="","",VLOOKUP($A92,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業務処理状況の報告義務あり</v>
       </c>
+      <c r="G92"/>
       <c r="I92" t="str">
         <f>IF($A92="","",VLOOKUP($A92,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業務処理状況の報告義務あり</v>
@@ -3979,13 +4068,13 @@
         <f>IF($A93="","",VLOOKUP($A93,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D93"/>
+      <c r="D93" s="5"/>
       <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" t="str">
+      <c r="F93" t="str">
         <f>IF($A93="","",VLOOKUP($A93,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介は2週間に1回以上</v>
       </c>
+      <c r="G93"/>
       <c r="I93" t="str">
         <f>IF($A93="","",VLOOKUP($A93,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>専任媒介は2週間に1回以上</v>
@@ -4003,13 +4092,13 @@
         <f>IF($A94="","",VLOOKUP($A94,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D94"/>
+      <c r="D94" s="5"/>
       <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-      <c r="G94" t="str">
+      <c r="F94" t="str">
         <f>IF($A94="","",VLOOKUP($A94,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介には報告義務はない</v>
       </c>
+      <c r="G94"/>
       <c r="I94" t="str">
         <f>IF($A94="","",VLOOKUP($A94,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一般媒介には報告義務はない</v>
@@ -4027,13 +4116,13 @@
         <f>IF($A95="","",VLOOKUP($A95,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D95"/>
+      <c r="D95" s="5"/>
       <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" t="str">
+      <c r="F95" t="str">
         <f>IF($A95="","",VLOOKUP($A95,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後5日以内に登録</v>
       </c>
+      <c r="G95"/>
       <c r="I95" t="str">
         <f>IF($A95="","",VLOOKUP($A95,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後5日以内に登録</v>
@@ -4051,13 +4140,13 @@
         <f>IF($A96="","",VLOOKUP($A96,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D96"/>
+      <c r="D96" s="5"/>
       <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" t="str">
+      <c r="F96" t="str">
         <f>IF($A96="","",VLOOKUP($A96,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後7日以内に登録</v>
       </c>
+      <c r="G96"/>
       <c r="I96" t="str">
         <f>IF($A96="","",VLOOKUP($A96,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>契約締結後7日以内に登録</v>
@@ -4075,13 +4164,13 @@
         <f>IF($A97="","",VLOOKUP($A97,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D97"/>
+      <c r="D97" s="5"/>
       <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" t="str">
+      <c r="F97" t="str">
         <f>IF($A97="","",VLOOKUP($A97,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付金等は代金の20%以内</v>
       </c>
+      <c r="G97"/>
       <c r="I97" t="str">
         <f>IF($A97="","",VLOOKUP($A97,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付金等は代金の20%以内</v>
@@ -4099,13 +4188,13 @@
         <f>IF($A98="","",VLOOKUP($A98,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D98"/>
+      <c r="D98" s="5"/>
       <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" t="str">
+      <c r="F98" t="str">
         <f>IF($A98="","",VLOOKUP($A98,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>特約がなければ解約手付</v>
       </c>
+      <c r="G98"/>
       <c r="I98" t="str">
         <f>IF($A98="","",VLOOKUP($A98,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>特約がなければ解約手付</v>
@@ -4123,13 +4212,13 @@
         <f>IF($A99="","",VLOOKUP($A99,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D99"/>
+      <c r="D99" s="5"/>
       <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" t="str">
+      <c r="F99" t="str">
         <f>IF($A99="","",VLOOKUP($A99,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>解約手付の原則</v>
       </c>
+      <c r="G99"/>
       <c r="I99" t="str">
         <f>IF($A99="","",VLOOKUP($A99,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>解約手付の原則</v>
@@ -4147,13 +4236,13 @@
         <f>IF($A100="","",VLOOKUP($A100,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D100"/>
+      <c r="D100" s="5"/>
       <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" t="str">
+      <c r="F100" t="str">
         <f>IF($A100="","",VLOOKUP($A100,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付倍返し</v>
       </c>
+      <c r="G100"/>
       <c r="I100" t="str">
         <f>IF($A100="","",VLOOKUP($A100,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>手付倍返し</v>
@@ -4171,13 +4260,13 @@
         <f>IF($A101="","",VLOOKUP($A101,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D101"/>
+      <c r="D101" s="5"/>
       <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" t="str">
+      <c r="F101" t="str">
         <f>IF($A101="","",VLOOKUP($A101,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>履行着手後は解除不可</v>
       </c>
+      <c r="G101"/>
       <c r="I101" t="str">
         <f>IF($A101="","",VLOOKUP($A101,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>履行着手後は解除不可</v>
@@ -4195,13 +4284,13 @@
         <f>IF($A102="","",VLOOKUP($A102,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D102"/>
+      <c r="D102" s="5"/>
       <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-      <c r="G102" t="str">
+      <c r="F102" t="str">
         <f>IF($A102="","",VLOOKUP($A102,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定の場合クーリングオフ可能</v>
       </c>
+      <c r="G102"/>
       <c r="I102" t="str">
         <f>IF($A102="","",VLOOKUP($A102,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定の場合クーリングオフ可能</v>
@@ -4219,13 +4308,13 @@
         <f>IF($A103="","",VLOOKUP($A103,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D103"/>
+      <c r="D103" s="5"/>
       <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" t="str">
+      <c r="F103" t="str">
         <f>IF($A103="","",VLOOKUP($A103,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>事務所契約は対象外</v>
       </c>
+      <c r="G103"/>
       <c r="I103" t="str">
         <f>IF($A103="","",VLOOKUP($A103,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>事務所契約は対象外</v>
@@ -4243,13 +4332,13 @@
         <f>IF($A104="","",VLOOKUP($A104,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D104"/>
+      <c r="D104" s="5"/>
       <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" t="str">
+      <c r="F104" t="str">
         <f>IF($A104="","",VLOOKUP($A104,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面受領から8日</v>
       </c>
+      <c r="G104"/>
       <c r="I104" t="str">
         <f>IF($A104="","",VLOOKUP($A104,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面受領から8日</v>
@@ -4267,13 +4356,13 @@
         <f>IF($A105="","",VLOOKUP($A105,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D105"/>
+      <c r="D105" s="5"/>
       <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" t="str">
+      <c r="F105" t="str">
         <f>IF($A105="","",VLOOKUP($A105,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面通知が必要</v>
       </c>
+      <c r="G105"/>
       <c r="I105" t="str">
         <f>IF($A105="","",VLOOKUP($A105,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>書面通知が必要</v>
@@ -4291,13 +4380,13 @@
         <f>IF($A106="","",VLOOKUP($A106,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D106"/>
+      <c r="D106" s="5"/>
       <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" t="str">
+      <c r="F106" t="str">
         <f>IF($A106="","",VLOOKUP($A106,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>損害賠償請求不可</v>
       </c>
+      <c r="G106"/>
       <c r="I106" t="str">
         <f>IF($A106="","",VLOOKUP($A106,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>損害賠償請求不可</v>
@@ -4315,13 +4404,13 @@
         <f>IF($A107="","",VLOOKUP($A107,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D107"/>
+      <c r="D107" s="5"/>
       <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" t="str">
+      <c r="F107" t="str">
         <f>IF($A107="","",VLOOKUP($A107,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金の20%以内</v>
       </c>
+      <c r="G107"/>
       <c r="I107" t="str">
         <f>IF($A107="","",VLOOKUP($A107,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金の20%以内</v>
@@ -4339,13 +4428,13 @@
         <f>IF($A108="","",VLOOKUP($A108,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D108"/>
+      <c r="D108" s="5"/>
       <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" t="str">
+      <c r="F108" t="str">
         <f>IF($A108="","",VLOOKUP($A108,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>合算して20%以内</v>
       </c>
+      <c r="G108"/>
       <c r="I108" t="str">
         <f>IF($A108="","",VLOOKUP($A108,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>合算して20%以内</v>
@@ -4363,13 +4452,13 @@
         <f>IF($A109="","",VLOOKUP($A109,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D109"/>
+      <c r="D109" s="5"/>
       <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" t="str">
+      <c r="F109" t="str">
         <f>IF($A109="","",VLOOKUP($A109,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>超過部分は無効</v>
       </c>
+      <c r="G109"/>
       <c r="I109" t="str">
         <f>IF($A109="","",VLOOKUP($A109,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>超過部分は無効</v>
@@ -4387,13 +4476,13 @@
         <f>IF($A110="","",VLOOKUP($A110,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D110"/>
+      <c r="D110" s="5"/>
       <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" t="str">
+      <c r="F110" t="str">
         <f>IF($A110="","",VLOOKUP($A110,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>2年以上</v>
       </c>
+      <c r="G110"/>
       <c r="I110" t="str">
         <f>IF($A110="","",VLOOKUP($A110,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>2年以上</v>
@@ -4411,13 +4500,13 @@
         <f>IF($A111="","",VLOOKUP($A111,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D111"/>
+      <c r="D111" s="5"/>
       <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" t="str">
+      <c r="F111" t="str">
         <f>IF($A111="","",VLOOKUP($A111,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主の場合不可</v>
       </c>
+      <c r="G111"/>
       <c r="I111" t="str">
         <f>IF($A111="","",VLOOKUP($A111,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>業者売主の場合不可</v>
@@ -4435,13 +4524,13 @@
         <f>IF($A112="","",VLOOKUP($A112,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D112"/>
+      <c r="D112" s="5"/>
       <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" t="str">
+      <c r="F112" t="str">
         <f>IF($A112="","",VLOOKUP($A112,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金完済まで留保</v>
       </c>
+      <c r="G112"/>
       <c r="I112" t="str">
         <f>IF($A112="","",VLOOKUP($A112,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>代金完済まで留保</v>
@@ -4459,13 +4548,13 @@
         <f>IF($A113="","",VLOOKUP($A113,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D113"/>
+      <c r="D113" s="5"/>
       <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-      <c r="G113" t="str">
+      <c r="F113" t="str">
         <f>IF($A113="","",VLOOKUP($A113,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間の催告が必要</v>
       </c>
+      <c r="G113"/>
       <c r="I113" t="str">
         <f>IF($A113="","",VLOOKUP($A113,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間の催告が必要</v>
@@ -4483,13 +4572,13 @@
         <f>IF($A114="","",VLOOKUP($A114,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D114"/>
+      <c r="D114" s="5"/>
       <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" t="str">
+      <c r="F114" t="str">
         <f>IF($A114="","",VLOOKUP($A114,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>30日以上</v>
       </c>
+      <c r="G114"/>
       <c r="I114" t="str">
         <f>IF($A114="","",VLOOKUP($A114,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>30日以上</v>
@@ -4507,13 +4596,13 @@
         <f>IF($A115="","",VLOOKUP($A115,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D115"/>
+      <c r="D115" s="5"/>
       <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-      <c r="G115" t="str">
+      <c r="F115" t="str">
         <f>IF($A115="","",VLOOKUP($A115,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>催告必要</v>
       </c>
+      <c r="G115"/>
       <c r="I115" t="str">
         <f>IF($A115="","",VLOOKUP($A115,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>催告必要</v>
@@ -4531,13 +4620,13 @@
         <f>IF($A116="","",VLOOKUP($A116,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D116"/>
+      <c r="D116" s="5"/>
       <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" t="str">
+      <c r="F116" t="str">
         <f>IF($A116="","",VLOOKUP($A116,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>融資不成立の場合解除</v>
       </c>
+      <c r="G116"/>
       <c r="I116" t="str">
         <f>IF($A116="","",VLOOKUP($A116,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>融資不成立の場合解除</v>
@@ -4555,13 +4644,13 @@
         <f>IF($A117="","",VLOOKUP($A117,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D117"/>
+      <c r="D117" s="5"/>
       <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" t="str">
+      <c r="F117" t="str">
         <f>IF($A117="","",VLOOKUP($A117,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>民法契約の特約</v>
       </c>
+      <c r="G117"/>
       <c r="I117" t="str">
         <f>IF($A117="","",VLOOKUP($A117,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>民法契約の特約</v>
@@ -4579,13 +4668,13 @@
         <f>IF($A118="","",VLOOKUP($A118,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D118"/>
+      <c r="D118" s="5"/>
       <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
-      <c r="G118" t="str">
+      <c r="F118" t="str">
         <f>IF($A118="","",VLOOKUP($A118,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>報酬規定あり</v>
       </c>
+      <c r="G118"/>
       <c r="I118" t="str">
         <f>IF($A118="","",VLOOKUP($A118,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>報酬規定あり</v>
@@ -4603,13 +4692,13 @@
         <f>IF($A119="","",VLOOKUP($A119,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D119"/>
+      <c r="D119" s="5"/>
       <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-      <c r="G119" t="str">
+      <c r="F119" t="str">
         <f>IF($A119="","",VLOOKUP($A119,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>=+消費税</v>
       </c>
+      <c r="G119"/>
       <c r="I119" t="str">
         <f>IF($A119="","",VLOOKUP($A119,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>=+消費税</v>
@@ -4627,13 +4716,13 @@
         <f>IF($A120="","",VLOOKUP($A120,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D120"/>
+      <c r="D120" s="5"/>
       <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-      <c r="G120" t="str">
+      <c r="F120" t="str">
         <f>IF($A120="","",VLOOKUP($A120,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>双方から受領可能</v>
       </c>
+      <c r="G120"/>
       <c r="I120" t="str">
         <f>IF($A120="","",VLOOKUP($A120,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>双方から受領可能</v>
@@ -4651,13 +4740,13 @@
         <f>IF($A121="","",VLOOKUP($A121,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>×</v>
       </c>
-      <c r="D121"/>
+      <c r="D121" s="5"/>
       <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" t="str">
+      <c r="F121" t="str">
         <f>IF($A121="","",VLOOKUP($A121,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>国土交通省告示で上限あり</v>
       </c>
+      <c r="G121"/>
       <c r="I121" t="str">
         <f>IF($A121="","",VLOOKUP($A121,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>国土交通省告示で上限あり</v>
@@ -4675,13 +4764,13 @@
         <f>IF($A122="","",VLOOKUP($A122,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D122"/>
+      <c r="D122" s="5"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-      <c r="G122" t="str">
+      <c r="F122" t="str">
         <f>IF($A122="","",VLOOKUP($A122,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>重大違反の場合</v>
       </c>
+      <c r="G122"/>
       <c r="I122" t="str">
         <f>IF($A122="","",VLOOKUP($A122,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>重大違反の場合</v>
@@ -4699,13 +4788,13 @@
         <f>IF($A123="","",VLOOKUP($A123,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D123"/>
+      <c r="D123" s="5"/>
       <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
-      <c r="G123" t="str">
+      <c r="F123" t="str">
         <f>IF($A123="","",VLOOKUP($A123,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間営業停止</v>
       </c>
+      <c r="G123"/>
       <c r="I123" t="str">
         <f>IF($A123="","",VLOOKUP($A123,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>一定期間営業停止</v>
@@ -4723,13 +4812,13 @@
         <f>IF($A124="","",VLOOKUP($A124,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D124"/>
+      <c r="D124" s="5"/>
       <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
-      <c r="G124" t="str">
+      <c r="F124" t="str">
         <f>IF($A124="","",VLOOKUP($A124,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>行政指導処分</v>
       </c>
+      <c r="G124"/>
       <c r="I124" t="str">
         <f>IF($A124="","",VLOOKUP($A124,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>行政指導処分</v>
@@ -4747,13 +4836,13 @@
         <f>IF($A125="","",VLOOKUP($A125,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D125"/>
+      <c r="D125" s="5"/>
       <c r="E125" s="5"/>
-      <c r="F125" s="5"/>
-      <c r="G125" t="str">
+      <c r="F125" t="str">
         <f>IF($A125="","",VLOOKUP($A125,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業法違反</v>
       </c>
+      <c r="G125"/>
       <c r="I125" t="str">
         <f>IF($A125="","",VLOOKUP($A125,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業法違反</v>
@@ -4771,13 +4860,13 @@
         <f>IF($A126="","",VLOOKUP($A126,データ宅建業法!$A$2:$E$500,4,FALSE))</f>
         <v>○</v>
       </c>
-      <c r="D126"/>
+      <c r="D126" s="5"/>
       <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
-      <c r="G126" t="str">
+      <c r="F126" t="str">
         <f>IF($A126="","",VLOOKUP($A126,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者の名義貸しは禁止</v>
       </c>
+      <c r="G126"/>
       <c r="I126" t="str">
         <f>IF($A126="","",VLOOKUP($A126,データ宅建業法!$A$2:$E$500,5,FALSE))</f>
         <v>宅建業者の名義貸しは禁止</v>
@@ -4794,7 +4883,34 @@
       <c r="C127" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="D127" s="10"/>
+      <c r="G127" s="10"/>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="str">
+        <f>"Q"&amp;ROW()-1</f>
+        <v>Q127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>426</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="str">
+        <f>IF(B129="","","Q"&amp;ROW()-1)</f>
+        <v>Q128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>428</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G129" t="s">
+        <v>430</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
